--- a/AuditTracker.xlsx
+++ b/AuditTracker.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Intelligence'!$A$1:$M$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Intelligence'!$A$1:$M$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Obligations'!$A$1:$O$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Actions'!$A$1:$L$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidence Gaps'!$A$1:$H$30</definedName>
@@ -420,7 +420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -633,6 +633,132 @@
     </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1445,29 +1571,29 @@
   <sheetData>
     <row r="1" ht="8" customHeight="1" s="28"/>
     <row r="2" ht="4" customHeight="1" s="28">
-      <c r="A2" s="75" t="n"/>
-      <c r="B2" s="75" t="n"/>
-      <c r="C2" s="75" t="n"/>
-      <c r="D2" s="75" t="n"/>
-      <c r="E2" s="75" t="n"/>
-      <c r="F2" s="75" t="n"/>
-      <c r="G2" s="75" t="n"/>
-      <c r="H2" s="75" t="n"/>
-      <c r="I2" s="75" t="n"/>
-      <c r="J2" s="75" t="n"/>
-      <c r="K2" s="75" t="n"/>
-      <c r="L2" s="75" t="n"/>
-      <c r="M2" s="75" t="n"/>
+      <c r="A2" s="117" t="n"/>
+      <c r="B2" s="117" t="n"/>
+      <c r="C2" s="117" t="n"/>
+      <c r="D2" s="117" t="n"/>
+      <c r="E2" s="117" t="n"/>
+      <c r="F2" s="117" t="n"/>
+      <c r="G2" s="117" t="n"/>
+      <c r="H2" s="117" t="n"/>
+      <c r="I2" s="117" t="n"/>
+      <c r="J2" s="117" t="n"/>
+      <c r="K2" s="117" t="n"/>
+      <c r="L2" s="117" t="n"/>
+      <c r="M2" s="117" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="28">
-      <c r="B3" s="76" t="inlineStr">
+      <c r="B3" s="118" t="inlineStr">
         <is>
           <t>NCC Audit Reform and LGR Obligations Tracker</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1" s="28">
-      <c r="B4" s="77" t="inlineStr">
+      <c r="B4" s="119" t="inlineStr">
         <is>
           <t>Live status snapshot  ·  Refreshed 04 August 2026</t>
         </is>
@@ -1475,42 +1601,42 @@
     </row>
     <row r="5" ht="12" customHeight="1" s="28"/>
     <row r="6" ht="6" customHeight="1" s="28">
-      <c r="B6" s="75" t="n"/>
-      <c r="E6" s="75" t="n"/>
-      <c r="H6" s="75" t="n"/>
-      <c r="K6" s="75" t="n"/>
+      <c r="B6" s="117" t="n"/>
+      <c r="E6" s="117" t="n"/>
+      <c r="H6" s="117" t="n"/>
+      <c r="K6" s="117" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1" s="28">
-      <c r="B7" s="78" t="n">
+      <c r="B7" s="120" t="n">
         <v>22</v>
       </c>
-      <c r="E7" s="79" t="n">
+      <c r="E7" s="121" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="80" t="n">
+      <c r="H7" s="122" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="80" t="n">
+      <c r="K7" s="122" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="28">
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="123" t="inlineStr">
         <is>
           <t>OBLIGATIONS</t>
         </is>
       </c>
-      <c r="E8" s="82" t="inlineStr">
+      <c r="E8" s="124" t="inlineStr">
         <is>
           <t>OVERDUE</t>
         </is>
       </c>
-      <c r="H8" s="83" t="inlineStr">
+      <c r="H8" s="125" t="inlineStr">
         <is>
           <t>DUE IN 30 DAYS</t>
         </is>
       </c>
-      <c r="K8" s="83" t="inlineStr">
+      <c r="K8" s="125" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -1518,7 +1644,7 @@
     </row>
     <row r="9" ht="14" customHeight="1" s="28"/>
     <row r="10" ht="20" customHeight="1" s="28">
-      <c r="B10" s="84" t="inlineStr">
+      <c r="B10" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">  OBLIGATIONS OVERVIEW</t>
         </is>
@@ -1526,181 +1652,181 @@
     </row>
     <row r="11" ht="8" customHeight="1" s="28"/>
     <row r="12" ht="16" customHeight="1" s="28">
-      <c r="B12" s="85" t="inlineStr">
+      <c r="B12" s="127" t="inlineStr">
         <is>
           <t>Obligations by Status</t>
         </is>
       </c>
-      <c r="F12" s="85" t="inlineStr">
+      <c r="F12" s="127" t="inlineStr">
         <is>
           <t>Obligations by Risk</t>
         </is>
       </c>
-      <c r="J12" s="85" t="inlineStr">
+      <c r="J12" s="127" t="inlineStr">
         <is>
           <t>Obligations by Theme</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="28">
-      <c r="B13" s="86" t="inlineStr">
+      <c r="B13" s="128" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
       <c r="C13" s="60" t="n"/>
-      <c r="D13" s="87" t="inlineStr">
+      <c r="D13" s="129" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="F13" s="86" t="inlineStr">
+      <c r="F13" s="128" t="inlineStr">
         <is>
           <t>Risk Rating</t>
         </is>
       </c>
       <c r="G13" s="60" t="n"/>
-      <c r="H13" s="87" t="inlineStr">
+      <c r="H13" s="129" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="J13" s="86" t="inlineStr">
+      <c r="J13" s="128" t="inlineStr">
         <is>
           <t>Theme</t>
         </is>
       </c>
       <c r="K13" s="60" t="n"/>
-      <c r="L13" s="87" t="inlineStr">
+      <c r="L13" s="129" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="28">
-      <c r="B14" s="88" t="inlineStr">
+      <c r="B14" s="130" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
       <c r="C14" s="60" t="n"/>
-      <c r="D14" s="89" t="n">
+      <c r="D14" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="88" t="inlineStr">
+      <c r="F14" s="130" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="G14" s="60" t="n"/>
-      <c r="H14" s="89" t="n">
+      <c r="H14" s="131" t="n">
         <v>17</v>
       </c>
-      <c r="J14" s="88" t="inlineStr">
+      <c r="J14" s="130" t="inlineStr">
         <is>
           <t>Governance and Transparency</t>
         </is>
       </c>
       <c r="K14" s="60" t="n"/>
-      <c r="L14" s="89" t="n">
+      <c r="L14" s="131" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="28">
-      <c r="B15" s="90" t="inlineStr">
+      <c r="B15" s="132" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
       <c r="C15" s="60" t="n"/>
-      <c r="D15" s="91" t="n">
+      <c r="D15" s="133" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="90" t="inlineStr">
+      <c r="F15" s="132" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="60" t="n"/>
-      <c r="H15" s="91" t="n">
+      <c r="H15" s="133" t="n">
         <v>5</v>
       </c>
-      <c r="J15" s="90" t="inlineStr">
+      <c r="J15" s="132" t="inlineStr">
         <is>
           <t>LGR Transition</t>
         </is>
       </c>
       <c r="K15" s="60" t="n"/>
-      <c r="L15" s="91" t="n">
+      <c r="L15" s="133" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="28">
-      <c r="B16" s="88" t="inlineStr">
+      <c r="B16" s="130" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
       <c r="C16" s="60" t="n"/>
-      <c r="D16" s="89" t="n">
+      <c r="D16" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="88" t="inlineStr">
+      <c r="F16" s="130" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="G16" s="60" t="n"/>
-      <c r="H16" s="89" t="n">
+      <c r="H16" s="131" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="88" t="inlineStr">
+      <c r="J16" s="130" t="inlineStr">
         <is>
           <t>Financial Reporting</t>
         </is>
       </c>
       <c r="K16" s="60" t="n"/>
-      <c r="L16" s="89" t="n">
+      <c r="L16" s="131" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="28">
-      <c r="B17" s="90" t="inlineStr">
+      <c r="B17" s="132" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
       <c r="C17" s="60" t="n"/>
-      <c r="D17" s="91" t="n">
+      <c r="D17" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="90" t="inlineStr">
+      <c r="J17" s="132" t="inlineStr">
         <is>
           <t>Audit Procurement</t>
         </is>
       </c>
       <c r="K17" s="60" t="n"/>
-      <c r="L17" s="91" t="n">
+      <c r="L17" s="133" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="28">
-      <c r="B18" s="88" t="inlineStr">
+      <c r="B18" s="130" t="inlineStr">
         <is>
           <t>Ongoing</t>
         </is>
       </c>
       <c r="C18" s="60" t="n"/>
-      <c r="D18" s="89" t="n">
+      <c r="D18" s="131" t="n">
         <v>8</v>
       </c>
-      <c r="J18" s="88" t="inlineStr">
+      <c r="J18" s="130" t="inlineStr">
         <is>
           <t>Internal Controls</t>
         </is>
       </c>
       <c r="K18" s="60" t="n"/>
-      <c r="L18" s="89" t="n">
+      <c r="L18" s="131" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1724,7 +1850,7 @@
     <row r="36" ht="15" customHeight="1" s="28"/>
     <row r="37" ht="14" customHeight="1" s="28"/>
     <row r="38" ht="20" customHeight="1" s="28">
-      <c r="B38" s="84" t="inlineStr">
+      <c r="B38" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">  ACTIONS &amp; INTELLIGENCE FEED</t>
         </is>
@@ -1732,143 +1858,143 @@
     </row>
     <row r="39" ht="8" customHeight="1" s="28"/>
     <row r="40" ht="18" customHeight="1" s="28">
-      <c r="B40" s="86" t="inlineStr">
+      <c r="B40" s="128" t="inlineStr">
         <is>
           <t>Action Summary</t>
         </is>
       </c>
       <c r="C40" s="60" t="n"/>
-      <c r="D40" s="87" t="inlineStr">
+      <c r="D40" s="129" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="F40" s="86" t="inlineStr">
+      <c r="F40" s="128" t="inlineStr">
         <is>
           <t>Intelligence Feed</t>
         </is>
       </c>
       <c r="G40" s="60" t="n"/>
-      <c r="H40" s="87" t="inlineStr">
+      <c r="H40" s="129" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="28">
-      <c r="B41" s="88" t="inlineStr">
+      <c r="B41" s="130" t="inlineStr">
         <is>
           <t>Total actions</t>
         </is>
       </c>
       <c r="C41" s="60" t="n"/>
-      <c r="D41" s="89" t="n">
+      <c r="D41" s="131" t="n">
         <v>32</v>
       </c>
-      <c r="F41" s="88" t="inlineStr">
+      <c r="F41" s="130" t="inlineStr">
         <is>
           <t>Items captured</t>
         </is>
       </c>
       <c r="G41" s="60" t="n"/>
-      <c r="H41" s="89" t="n">
-        <v>130</v>
+      <c r="H41" s="131" t="n">
+        <v>208</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="28">
-      <c r="B42" s="90" t="inlineStr">
+      <c r="B42" s="132" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
       <c r="C42" s="60" t="n"/>
-      <c r="D42" s="91" t="n">
+      <c r="D42" s="133" t="n">
         <v>10</v>
       </c>
-      <c r="F42" s="90" t="inlineStr">
+      <c r="F42" s="132" t="inlineStr">
         <is>
           <t>Flagged material</t>
         </is>
       </c>
       <c r="G42" s="60" t="n"/>
-      <c r="H42" s="91" t="n">
-        <v>43</v>
+      <c r="H42" s="133" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="28">
-      <c r="B43" s="88" t="inlineStr">
+      <c r="B43" s="130" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
       <c r="C43" s="60" t="n"/>
-      <c r="D43" s="89" t="n">
+      <c r="D43" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="88" t="inlineStr">
+      <c r="F43" s="130" t="inlineStr">
         <is>
           <t>Material (last 30 days)</t>
         </is>
       </c>
       <c r="G43" s="60" t="n"/>
-      <c r="H43" s="89" t="n">
-        <v>13</v>
+      <c r="H43" s="131" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="28">
-      <c r="B44" s="90" t="inlineStr">
+      <c r="B44" s="132" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
       <c r="C44" s="60" t="n"/>
-      <c r="D44" s="91" t="n">
+      <c r="D44" s="133" t="n">
         <v>7</v>
       </c>
-      <c r="F44" s="90" t="inlineStr">
+      <c r="F44" s="132" t="inlineStr">
         <is>
           <t>Awaiting review</t>
         </is>
       </c>
       <c r="G44" s="60" t="n"/>
-      <c r="H44" s="91" t="n">
-        <v>58</v>
+      <c r="H44" s="133" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="28">
-      <c r="B45" s="88" t="inlineStr">
+      <c r="B45" s="130" t="inlineStr">
         <is>
           <t>Avg. progress</t>
         </is>
       </c>
       <c r="C45" s="60" t="n"/>
-      <c r="D45" s="89" t="inlineStr">
+      <c r="D45" s="131" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="28">
-      <c r="B46" s="90" t="inlineStr">
+      <c r="B46" s="132" t="inlineStr">
         <is>
           <t>Evidence coverage</t>
         </is>
       </c>
       <c r="C46" s="60" t="n"/>
-      <c r="D46" s="91" t="inlineStr">
+      <c r="D46" s="133" t="inlineStr">
         <is>
           <t>22% (7/32)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="28">
-      <c r="B47" s="88" t="inlineStr">
+      <c r="B47" s="130" t="inlineStr">
         <is>
           <t>Evidence at completion</t>
         </is>
       </c>
       <c r="C47" s="60" t="n"/>
-      <c r="D47" s="89" t="inlineStr">
+      <c r="D47" s="131" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1876,7 +2002,7 @@
     </row>
     <row r="48" ht="14" customHeight="1" s="28"/>
     <row r="49" ht="20" customHeight="1" s="28">
-      <c r="B49" s="84" t="inlineStr">
+      <c r="B49" s="126" t="inlineStr">
         <is>
           <t xml:space="preserve">  ATTENTION NEEDED</t>
         </is>
@@ -1884,12 +2010,12 @@
     </row>
     <row r="50" ht="8" customHeight="1" s="28"/>
     <row r="51" ht="18" customHeight="1" s="28">
-      <c r="B51" s="86" t="inlineStr">
+      <c r="B51" s="128" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C51" s="86" t="inlineStr">
+      <c r="C51" s="128" t="inlineStr">
         <is>
           <t>Obligation</t>
         </is>
@@ -1899,26 +2025,26 @@
       <c r="F51" s="66" t="n"/>
       <c r="G51" s="66" t="n"/>
       <c r="H51" s="60" t="n"/>
-      <c r="I51" s="86" t="inlineStr">
+      <c r="I51" s="128" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
       <c r="J51" s="66" t="n"/>
       <c r="K51" s="60" t="n"/>
-      <c r="L51" s="86" t="inlineStr">
+      <c r="L51" s="128" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M51" s="86" t="inlineStr">
+      <c r="M51" s="128" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1" s="28">
-      <c r="B52" s="92" t="inlineStr">
+      <c r="B52" s="134" t="inlineStr">
         <is>
           <t>OB-A2</t>
         </is>
@@ -1940,19 +2066,19 @@
       </c>
       <c r="J52" s="66" t="n"/>
       <c r="K52" s="60" t="n"/>
-      <c r="L52" s="88" t="inlineStr">
+      <c r="L52" s="130" t="inlineStr">
         <is>
           <t>24 Jun 2026</t>
         </is>
       </c>
-      <c r="M52" s="93" t="inlineStr">
+      <c r="M52" s="135" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="53" ht="34" customHeight="1" s="28">
-      <c r="B53" s="94" t="inlineStr">
+      <c r="B53" s="136" t="inlineStr">
         <is>
           <t>OB-A7</t>
         </is>
@@ -1974,19 +2100,19 @@
       </c>
       <c r="J53" s="66" t="n"/>
       <c r="K53" s="60" t="n"/>
-      <c r="L53" s="90" t="inlineStr">
+      <c r="L53" s="132" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="M53" s="95" t="inlineStr">
+      <c r="M53" s="137" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="54" ht="34" customHeight="1" s="28">
-      <c r="B54" s="92" t="inlineStr">
+      <c r="B54" s="134" t="inlineStr">
         <is>
           <t>OB-A9</t>
         </is>
@@ -2008,19 +2134,19 @@
       </c>
       <c r="J54" s="66" t="n"/>
       <c r="K54" s="60" t="n"/>
-      <c r="L54" s="88" t="inlineStr">
+      <c r="L54" s="130" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="M54" s="93" t="inlineStr">
+      <c r="M54" s="135" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="55" ht="34" customHeight="1" s="28">
-      <c r="B55" s="94" t="inlineStr">
+      <c r="B55" s="136" t="inlineStr">
         <is>
           <t>OB-A11</t>
         </is>
@@ -2042,19 +2168,19 @@
       </c>
       <c r="J55" s="66" t="n"/>
       <c r="K55" s="60" t="n"/>
-      <c r="L55" s="90" t="inlineStr">
+      <c r="L55" s="132" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="M55" s="95" t="inlineStr">
+      <c r="M55" s="137" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="56" ht="34" customHeight="1" s="28">
-      <c r="B56" s="92" t="inlineStr">
+      <c r="B56" s="134" t="inlineStr">
         <is>
           <t>OB-L5</t>
         </is>
@@ -2076,12 +2202,12 @@
       </c>
       <c r="J56" s="66" t="n"/>
       <c r="K56" s="60" t="n"/>
-      <c r="L56" s="88" t="inlineStr">
+      <c r="L56" s="130" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="M56" s="93" t="inlineStr">
+      <c r="M56" s="135" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
@@ -2089,19 +2215,19 @@
     </row>
     <row r="57" ht="10" customHeight="1" s="28"/>
     <row r="58" ht="4" customHeight="1" s="28">
-      <c r="A58" s="75" t="n"/>
-      <c r="B58" s="75" t="n"/>
-      <c r="C58" s="75" t="n"/>
-      <c r="D58" s="75" t="n"/>
-      <c r="E58" s="75" t="n"/>
-      <c r="F58" s="75" t="n"/>
-      <c r="G58" s="75" t="n"/>
-      <c r="H58" s="75" t="n"/>
-      <c r="I58" s="75" t="n"/>
-      <c r="J58" s="75" t="n"/>
-      <c r="K58" s="75" t="n"/>
-      <c r="L58" s="75" t="n"/>
-      <c r="M58" s="75" t="n"/>
+      <c r="A58" s="117" t="n"/>
+      <c r="B58" s="117" t="n"/>
+      <c r="C58" s="117" t="n"/>
+      <c r="D58" s="117" t="n"/>
+      <c r="E58" s="117" t="n"/>
+      <c r="F58" s="117" t="n"/>
+      <c r="G58" s="117" t="n"/>
+      <c r="H58" s="117" t="n"/>
+      <c r="I58" s="117" t="n"/>
+      <c r="J58" s="117" t="n"/>
+      <c r="K58" s="117" t="n"/>
+      <c r="L58" s="117" t="n"/>
+      <c r="M58" s="117" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="61">
@@ -2178,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="28" min="1" max="1"/>
@@ -9705,8 +9831,4314 @@
       </c>
       <c r="M131" s="46" t="n"/>
     </row>
+    <row r="132" ht="40" customHeight="1" s="28">
+      <c r="A132" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B132" s="44" t="inlineStr">
+        <is>
+          <t>Local Government Pension Scheme administering authorities: local government reorganisation</t>
+        </is>
+      </c>
+      <c r="C132" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D132" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E132" s="43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="F132" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G132" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H132" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I132" s="44" t="inlineStr">
+        <is>
+          <t>/government/publications/local-government-pension-scheme-administering-authorities-local-government-reorganisation/local-government-pension-scheme-administering-authorities-local-government-reorganisation</t>
+        </is>
+      </c>
+      <c r="J132" s="43" t="inlineStr"/>
+      <c r="K132" s="44" t="inlineStr"/>
+      <c r="L132" s="44" t="inlineStr">
+        <is>
+          <t>db64c6563818b46ba1012f37a74edecb</t>
+        </is>
+      </c>
+      <c r="M132" s="44" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1" s="28">
+      <c r="A133" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B133" s="46" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: staffing issues guidance</t>
+        </is>
+      </c>
+      <c r="C133" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D133" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E133" s="45" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F133" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G133" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H133" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I133" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a58f75b24d4d0ad06d94627/LGR_Staffing_Issues_Guidance.pdf</t>
+        </is>
+      </c>
+      <c r="J133" s="45" t="inlineStr"/>
+      <c r="K133" s="46" t="inlineStr"/>
+      <c r="L133" s="46" t="inlineStr">
+        <is>
+          <t>f39506aa245d02927dd42bbdfe0310b6</t>
+        </is>
+      </c>
+      <c r="M133" s="46" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1" s="28">
+      <c r="A134" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B134" s="44" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: staffing issues guidance overview</t>
+        </is>
+      </c>
+      <c r="C134" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D134" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E134" s="43" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F134" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G134" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H134" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I134" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a58d69b908b618a53702f04/Local_government_reorganisation_-_staffing_issues_guidance_overview.pdf</t>
+        </is>
+      </c>
+      <c r="J134" s="43" t="inlineStr"/>
+      <c r="K134" s="44" t="inlineStr"/>
+      <c r="L134" s="44" t="inlineStr">
+        <is>
+          <t>86d92d34bceef52fe5b627fff74051a0</t>
+        </is>
+      </c>
+      <c r="M134" s="44" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1" s="28">
+      <c r="A135" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B135" s="46" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: guidance on sector support</t>
+        </is>
+      </c>
+      <c r="C135" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D135" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E135" s="45" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F135" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G135" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H135" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I135" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a58a7452f6185941a9a6647/Local_government_reorganisation_-_sector_support_guidance.pdf</t>
+        </is>
+      </c>
+      <c r="J135" s="45" t="inlineStr"/>
+      <c r="K135" s="46" t="inlineStr"/>
+      <c r="L135" s="46" t="inlineStr">
+        <is>
+          <t>eabdca899e75b10c3f91ee83057bae71</t>
+        </is>
+      </c>
+      <c r="M135" s="46" t="inlineStr"/>
+    </row>
+    <row r="136" ht="40" customHeight="1" s="28">
+      <c r="A136" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B136" s="44" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: implementation guidance for the first transition period</t>
+        </is>
+      </c>
+      <c r="C136" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D136" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E136" s="43" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F136" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G136" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H136" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I136" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69b1a416cdd628b29e349705/Local_government_reorganisation_-_implementation_guidance.pdf</t>
+        </is>
+      </c>
+      <c r="J136" s="43" t="inlineStr"/>
+      <c r="K136" s="44" t="inlineStr"/>
+      <c r="L136" s="44" t="inlineStr">
+        <is>
+          <t>bbb4a9c71e2ea227048901ed55969917</t>
+        </is>
+      </c>
+      <c r="M136" s="44" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1" s="28">
+      <c r="A137" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B137" s="46" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: implementation guidance for the second transition period</t>
+        </is>
+      </c>
+      <c r="C137" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D137" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E137" s="45" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F137" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G137" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H137" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I137" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a0eeefc9c0df135284ec7ae/Local_government_reorganisation_-_implementation_guidance_for_the_second_transition_period.pdf</t>
+        </is>
+      </c>
+      <c r="J137" s="45" t="inlineStr"/>
+      <c r="K137" s="46" t="inlineStr"/>
+      <c r="L137" s="46" t="inlineStr">
+        <is>
+          <t>54c000e984637d9b46caaed5e0b2958b</t>
+        </is>
+      </c>
+      <c r="M137" s="46" t="inlineStr"/>
+    </row>
+    <row r="138" ht="40" customHeight="1" s="28">
+      <c r="A138" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B138" s="44" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: summary of feedback on interim plans</t>
+        </is>
+      </c>
+      <c r="C138" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D138" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E138" s="43" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="F138" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G138" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H138" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I138" s="44" t="inlineStr">
+        <is>
+          <t>/government/publications/local-government-reorganisation-summary-of-feedback-on-interim-plans/local-government-reorganisation-summary-of-feedback-on-interim-plans</t>
+        </is>
+      </c>
+      <c r="J138" s="43" t="inlineStr"/>
+      <c r="K138" s="44" t="inlineStr"/>
+      <c r="L138" s="44" t="inlineStr">
+        <is>
+          <t>81eb402569d1df2510c023e510b7e5fd</t>
+        </is>
+      </c>
+      <c r="M138" s="44" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1" s="28">
+      <c r="A139" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B139" s="46" t="inlineStr">
+        <is>
+          <t>English Devolution White Paper</t>
+        </is>
+      </c>
+      <c r="C139" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D139" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E139" s="45" t="inlineStr">
+        <is>
+          <t>2024-12-16</t>
+        </is>
+      </c>
+      <c r="F139" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G139" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H139" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I139" s="46" t="inlineStr">
+        <is>
+          <t>/government/publications/english-devolution-white-paper-power-and-partnership-foundations-for-growth/english-devolution-white-paper</t>
+        </is>
+      </c>
+      <c r="J139" s="45" t="inlineStr"/>
+      <c r="K139" s="46" t="inlineStr"/>
+      <c r="L139" s="46" t="inlineStr">
+        <is>
+          <t>09e260469495b3c018781499a703a588</t>
+        </is>
+      </c>
+      <c r="M139" s="46" t="inlineStr"/>
+    </row>
+    <row r="140" ht="40" customHeight="1" s="28">
+      <c r="A140" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B140" s="44" t="inlineStr">
+        <is>
+          <t>English Devolution White Paper</t>
+        </is>
+      </c>
+      <c r="C140" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D140" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E140" s="43" t="inlineStr">
+        <is>
+          <t>2024-12-16</t>
+        </is>
+      </c>
+      <c r="F140" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G140" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H140" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I140" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/67ade9866e6c8d18118acd58/English_Devolution_White_Paper_Web_Accessible.pdf</t>
+        </is>
+      </c>
+      <c r="J140" s="43" t="inlineStr"/>
+      <c r="K140" s="44" t="inlineStr"/>
+      <c r="L140" s="44" t="inlineStr">
+        <is>
+          <t>f4510012e08feda08cae1d99ad3df59e</t>
+        </is>
+      </c>
+      <c r="M140" s="44" t="inlineStr"/>
+    </row>
+    <row r="141" ht="40" customHeight="1" s="28">
+      <c r="A141" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B141" s="46" t="inlineStr">
+        <is>
+          <t>Letter to council leaders: update on Secretary of State's decision regarding local elections of May 2026</t>
+        </is>
+      </c>
+      <c r="C141" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D141" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E141" s="45" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="F141" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G141" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H141" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I141" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/699328da7da91680ad7f44a9/update_on_secretary_of_state_s_decision_regarding_local_elections_of_may_2026_-_letter_to_council_leaders.pdf</t>
+        </is>
+      </c>
+      <c r="J141" s="45" t="inlineStr"/>
+      <c r="K141" s="46" t="inlineStr"/>
+      <c r="L141" s="46" t="inlineStr">
+        <is>
+          <t>3c86e7aa79ba15032b729f3217637941</t>
+        </is>
+      </c>
+      <c r="M141" s="46" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1" s="28">
+      <c r="A142" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B142" s="44" t="inlineStr">
+        <is>
+          <t>Letter to Pendle Borough Council</t>
+        </is>
+      </c>
+      <c r="C142" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D142" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E142" s="43" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="F142" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G142" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H142" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I142" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/697b3799b28b2cc262572ef3/Letter_to_Pendle_Borough_Council.pdf</t>
+        </is>
+      </c>
+      <c r="J142" s="43" t="inlineStr"/>
+      <c r="K142" s="44" t="inlineStr"/>
+      <c r="L142" s="44" t="inlineStr">
+        <is>
+          <t>c02ac374d257069f0ea849fa80219338</t>
+        </is>
+      </c>
+      <c r="M142" s="44" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1" s="28">
+      <c r="A143" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B143" s="46" t="inlineStr">
+        <is>
+          <t>Letter to council leaders on the postponement of May 2026 local elections</t>
+        </is>
+      </c>
+      <c r="C143" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D143" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E143" s="45" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="F143" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G143" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H143" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I143" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69720b4ca1311bdcfa0ed8ab/Letter_to_Council_Leaders_on_postponement_of_local_elections_in_May_2026.pdf</t>
+        </is>
+      </c>
+      <c r="J143" s="45" t="inlineStr"/>
+      <c r="K143" s="46" t="inlineStr"/>
+      <c r="L143" s="46" t="inlineStr">
+        <is>
+          <t>7f5b1249783a65c2e3ee3ba440afa0fd</t>
+        </is>
+      </c>
+      <c r="M143" s="46" t="inlineStr"/>
+    </row>
+    <row r="144" ht="40" customHeight="1" s="28">
+      <c r="A144" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B144" s="44" t="inlineStr">
+        <is>
+          <t>Letter to leader of Oxford City Council</t>
+        </is>
+      </c>
+      <c r="C144" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D144" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E144" s="43" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F144" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G144" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H144" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I144" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/696e1a4f091f0cc41e81a24b/Letter_to_leader_of_Oxford_City_Council.pdf</t>
+        </is>
+      </c>
+      <c r="J144" s="43" t="inlineStr"/>
+      <c r="K144" s="44" t="inlineStr"/>
+      <c r="L144" s="44" t="inlineStr">
+        <is>
+          <t>2524783ce18e0a6978e2c132a8b17d02</t>
+        </is>
+      </c>
+      <c r="M144" s="44" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1" s="28">
+      <c r="A145" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B145" s="46" t="inlineStr">
+        <is>
+          <t>Letter to leader of Southampton City Council</t>
+        </is>
+      </c>
+      <c r="C145" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D145" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E145" s="45" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F145" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G145" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H145" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I145" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/696e1a9da426b80193afc7fe/Letter_to_leader_of_Southampton_City_Council.pdf</t>
+        </is>
+      </c>
+      <c r="J145" s="45" t="inlineStr"/>
+      <c r="K145" s="46" t="inlineStr"/>
+      <c r="L145" s="46" t="inlineStr">
+        <is>
+          <t>1b163337356b2ca5ac74cb2f58ec8df6</t>
+        </is>
+      </c>
+      <c r="M145" s="46" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1" s="28">
+      <c r="A146" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B146" s="44" t="inlineStr">
+        <is>
+          <t>Letter to council leaders with elections in May 2026</t>
+        </is>
+      </c>
+      <c r="C146" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D146" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E146" s="43" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="F146" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G146" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H146" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I146" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6944196136f089d38be1f31a/lgr-letter-councils-elections-may-2026.pdf</t>
+        </is>
+      </c>
+      <c r="J146" s="43" t="inlineStr"/>
+      <c r="K146" s="44" t="inlineStr"/>
+      <c r="L146" s="44" t="inlineStr">
+        <is>
+          <t>e4f385faea14eb07dd43377a034ae032</t>
+        </is>
+      </c>
+      <c r="M146" s="44" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1" s="28">
+      <c r="A147" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B147" s="46" t="inlineStr">
+        <is>
+          <t>Letter to council leader on the publicity code</t>
+        </is>
+      </c>
+      <c r="C147" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D147" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E147" s="45" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="F147" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G147" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H147" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I147" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/691dde2f513046b952c500af/Letter_to_Leaders_on_Publicity_Code_and_Local_Government_Reorganisation.pdf</t>
+        </is>
+      </c>
+      <c r="J147" s="45" t="inlineStr"/>
+      <c r="K147" s="46" t="inlineStr"/>
+      <c r="L147" s="46" t="inlineStr">
+        <is>
+          <t>9b8895f9a5e3963b18c575962e3b9050</t>
+        </is>
+      </c>
+      <c r="M147" s="46" t="inlineStr"/>
+    </row>
+    <row r="148" ht="40" customHeight="1" s="28">
+      <c r="A148" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B148" s="44" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: letter to areas invited to submit final proposals</t>
+        </is>
+      </c>
+      <c r="C148" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D148" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E148" s="43" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="F148" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G148" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H148" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I148" s="44" t="inlineStr">
+        <is>
+          <t>/government/publications/local-government-reorganisation-letter-to-areas-invited-to-submitted-final-proposals/local-government-reorganisation-letter-to-areas-invited-to-submitted-final-proposals</t>
+        </is>
+      </c>
+      <c r="J148" s="43" t="inlineStr"/>
+      <c r="K148" s="44" t="inlineStr"/>
+      <c r="L148" s="44" t="inlineStr">
+        <is>
+          <t>2bded096ec6af781c7ec3e4d20e236bc</t>
+        </is>
+      </c>
+      <c r="M148" s="44" t="inlineStr"/>
+    </row>
+    <row r="149" ht="40" customHeight="1" s="28">
+      <c r="A149" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B149" s="46" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: Considerations for partnership working in social care for new unitary authorities</t>
+        </is>
+      </c>
+      <c r="C149" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D149" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E149" s="45" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="F149" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G149" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H149" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I149" s="46" t="inlineStr">
+        <is>
+          <t>/government/publications/local-government-reorganisation-letter-to-areas-invited-to-submitted-final-proposals/local-government-reorganisation-considerations-for-partnership-working-in-social-care-for-new-unitary-authorities</t>
+        </is>
+      </c>
+      <c r="J149" s="45" t="inlineStr"/>
+      <c r="K149" s="46" t="inlineStr"/>
+      <c r="L149" s="46" t="inlineStr">
+        <is>
+          <t>88dbe6cf11d66c4e37fd7908b3f74466</t>
+        </is>
+      </c>
+      <c r="M149" s="46" t="inlineStr"/>
+    </row>
+    <row r="150" ht="40" customHeight="1" s="28">
+      <c r="A150" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B150" s="44" t="inlineStr">
+        <is>
+          <t>Summary of the local government reorganisation process</t>
+        </is>
+      </c>
+      <c r="C150" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D150" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E150" s="43" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="F150" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G150" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H150" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I150" s="44" t="inlineStr">
+        <is>
+          <t>/government/publications/local-government-reorganisation-letter-to-areas-invited-to-submitted-final-proposals/summary-of-the-local-government-reorganisation-process</t>
+        </is>
+      </c>
+      <c r="J150" s="43" t="inlineStr"/>
+      <c r="K150" s="44" t="inlineStr"/>
+      <c r="L150" s="44" t="inlineStr">
+        <is>
+          <t>363996639d432ab1f1b8904a0c3ecd02</t>
+        </is>
+      </c>
+      <c r="M150" s="44" t="inlineStr"/>
+    </row>
+    <row r="151" ht="40" customHeight="1" s="28">
+      <c r="A151" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B151" s="46" t="inlineStr">
+        <is>
+          <t>Financial decisions before local government reorganisation</t>
+        </is>
+      </c>
+      <c r="C151" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D151" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E151" s="45" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="F151" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G151" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H151" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I151" s="46" t="inlineStr">
+        <is>
+          <t>/government/publications/local-government-reorganisation-letter-to-areas-invited-to-submitted-final-proposals/financial-decisions-before-local-government-reorganisation</t>
+        </is>
+      </c>
+      <c r="J151" s="45" t="inlineStr"/>
+      <c r="K151" s="46" t="inlineStr"/>
+      <c r="L151" s="46" t="inlineStr">
+        <is>
+          <t>6a4a8336d5645c502d3fd8326204efa5</t>
+        </is>
+      </c>
+      <c r="M151" s="46" t="inlineStr"/>
+    </row>
+    <row r="152" ht="40" customHeight="1" s="28">
+      <c r="A152" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B152" s="44" t="inlineStr">
+        <is>
+          <t>Nottinghamshire and Nottingham</t>
+        </is>
+      </c>
+      <c r="C152" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D152" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E152" s="43" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="F152" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G152" s="44" t="inlineStr">
+        <is>
+          <t>Local, Transition</t>
+        </is>
+      </c>
+      <c r="H152" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I152" s="44" t="inlineStr">
+        <is>
+          <t>/government/publications/local-government-reorganisation-invitation-to-local-authorities-in-two-tier-areas/nottinghamshire-and-nottingham</t>
+        </is>
+      </c>
+      <c r="J152" s="43" t="inlineStr"/>
+      <c r="K152" s="44" t="inlineStr"/>
+      <c r="L152" s="44" t="inlineStr">
+        <is>
+          <t>f2077f587d88ce4ffdbe198a8e816e98</t>
+        </is>
+      </c>
+      <c r="M152" s="44" t="inlineStr"/>
+    </row>
+    <row r="153" ht="40" customHeight="1" s="28">
+      <c r="A153" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B153" s="46" t="inlineStr">
+        <is>
+          <t>Letter from Jim McMahon, Minister for Local Government and English Devolution (16 December 2024)</t>
+        </is>
+      </c>
+      <c r="C153" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D153" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E153" s="45" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="F153" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G153" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H153" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I153" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/67864788f041702a11ca0f44/Local_government_reorganisation_-_letter_to_two-tier_areas.pdf</t>
+        </is>
+      </c>
+      <c r="J153" s="45" t="inlineStr"/>
+      <c r="K153" s="46" t="inlineStr"/>
+      <c r="L153" s="46" t="inlineStr">
+        <is>
+          <t>bf0f43be0abe9545716d6f8155796eaf</t>
+        </is>
+      </c>
+      <c r="M153" s="46" t="inlineStr"/>
+    </row>
+    <row r="154" ht="40" customHeight="1" s="28">
+      <c r="A154" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B154" s="44" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation (LGR) Advisory Group 12 May 2025</t>
+        </is>
+      </c>
+      <c r="C154" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D154" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E154" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F154" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G154" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H154" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I154" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/68834b9ebe2291b14d11aee6/Local_Government_Reorganisation_Advisory_Group_12_May_2025.pdf</t>
+        </is>
+      </c>
+      <c r="J154" s="43" t="inlineStr"/>
+      <c r="K154" s="44" t="inlineStr"/>
+      <c r="L154" s="44" t="inlineStr">
+        <is>
+          <t>71554a1fad9a19e033a4581981496e2f</t>
+        </is>
+      </c>
+      <c r="M154" s="44" t="inlineStr"/>
+    </row>
+    <row r="155" ht="40" customHeight="1" s="28">
+      <c r="A155" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B155" s="46" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation (LGR) Advisory Group 3 September 2025</t>
+        </is>
+      </c>
+      <c r="C155" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D155" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E155" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F155" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G155" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H155" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I155" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/690386535c84b1206832a89c/LGR_Advisory_Group_Meeting_Summary_3_September.pdf</t>
+        </is>
+      </c>
+      <c r="J155" s="45" t="inlineStr"/>
+      <c r="K155" s="46" t="inlineStr"/>
+      <c r="L155" s="46" t="inlineStr">
+        <is>
+          <t>5bb4038044a04e13d53345d49f83eabb</t>
+        </is>
+      </c>
+      <c r="M155" s="46" t="inlineStr"/>
+    </row>
+    <row r="156" ht="40" customHeight="1" s="28">
+      <c r="A156" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B156" s="44" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation (LGR) Advisory Group 6 October 2025</t>
+        </is>
+      </c>
+      <c r="C156" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D156" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E156" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F156" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G156" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H156" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I156" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/690386695c84b1206832a89d/October_Advisory_Group_Short_Summary.pdf</t>
+        </is>
+      </c>
+      <c r="J156" s="43" t="inlineStr"/>
+      <c r="K156" s="44" t="inlineStr"/>
+      <c r="L156" s="44" t="inlineStr">
+        <is>
+          <t>d68e5618875880643c4a5820f54f2388</t>
+        </is>
+      </c>
+      <c r="M156" s="44" t="inlineStr"/>
+    </row>
+    <row r="157" ht="40" customHeight="1" s="28">
+      <c r="A157" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B157" s="46" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation Advisory Group – Terms of Reference and membership</t>
+        </is>
+      </c>
+      <c r="C157" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D157" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E157" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F157" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G157" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H157" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I157" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/690387655c84b1206832a89e/LGR_AG_Terms_of_Reference_and_membership.pdf</t>
+        </is>
+      </c>
+      <c r="J157" s="45" t="inlineStr"/>
+      <c r="K157" s="46" t="inlineStr"/>
+      <c r="L157" s="46" t="inlineStr">
+        <is>
+          <t>41e699f0548aef37fb1ff772c0247d00</t>
+        </is>
+      </c>
+      <c r="M157" s="46" t="inlineStr"/>
+    </row>
+    <row r="158" ht="40" customHeight="1" s="28">
+      <c r="A158" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B158" s="44" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation Advisory Group 6 November 2025</t>
+        </is>
+      </c>
+      <c r="C158" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D158" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E158" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F158" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G158" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H158" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I158" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/697cc7a7edc921ef1a245284/Local_Government_Reorganisation__LGR__Advisory_Group__November_6_2025.pdf</t>
+        </is>
+      </c>
+      <c r="J158" s="43" t="inlineStr"/>
+      <c r="K158" s="44" t="inlineStr"/>
+      <c r="L158" s="44" t="inlineStr">
+        <is>
+          <t>cebb010c1e2ec0e1db39779bb8ed6a0a</t>
+        </is>
+      </c>
+      <c r="M158" s="44" t="inlineStr"/>
+    </row>
+    <row r="159" ht="40" customHeight="1" s="28">
+      <c r="A159" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B159" s="46" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation Advisory Group 4 December 2025</t>
+        </is>
+      </c>
+      <c r="C159" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D159" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E159" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F159" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G159" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H159" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I159" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/697cc85f3915f7123658004d/Local_Government_Reorganisation_Advisory_Group_4_December_2025.pdf</t>
+        </is>
+      </c>
+      <c r="J159" s="45" t="inlineStr"/>
+      <c r="K159" s="46" t="inlineStr"/>
+      <c r="L159" s="46" t="inlineStr">
+        <is>
+          <t>4bb6970b6bd45aa2abeaa1c1c99034f4</t>
+        </is>
+      </c>
+      <c r="M159" s="46" t="inlineStr"/>
+    </row>
+    <row r="160" ht="40" customHeight="1" s="28">
+      <c r="A160" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B160" s="44" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation Advisory Group 13 January 2026</t>
+        </is>
+      </c>
+      <c r="C160" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D160" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E160" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F160" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G160" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H160" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I160" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/697cc95084f2153b11245288/Local_Government_Reorganisation_Advisory_Group_13_January_2026.pdf</t>
+        </is>
+      </c>
+      <c r="J160" s="43" t="inlineStr"/>
+      <c r="K160" s="44" t="inlineStr"/>
+      <c r="L160" s="44" t="inlineStr">
+        <is>
+          <t>80d720500b4dd5ea7e56924c2f842b3e</t>
+        </is>
+      </c>
+      <c r="M160" s="44" t="inlineStr"/>
+    </row>
+    <row r="161" ht="40" customHeight="1" s="28">
+      <c r="A161" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B161" s="46" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation Advisory Group 12 February 2026</t>
+        </is>
+      </c>
+      <c r="C161" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D161" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E161" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F161" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G161" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H161" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I161" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/699ecf713e672177d0bc762d/20260217_LGRAG_February_Meeting_Short_Summary__1_.pdf</t>
+        </is>
+      </c>
+      <c r="J161" s="45" t="inlineStr"/>
+      <c r="K161" s="46" t="inlineStr"/>
+      <c r="L161" s="46" t="inlineStr">
+        <is>
+          <t>d39e13b8901cfd1bfa4a371e0f6b9047</t>
+        </is>
+      </c>
+      <c r="M161" s="46" t="inlineStr"/>
+    </row>
+    <row r="162" ht="40" customHeight="1" s="28">
+      <c r="A162" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B162" s="44" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation Advisory Group 18 March 2026</t>
+        </is>
+      </c>
+      <c r="C162" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D162" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E162" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F162" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G162" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H162" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I162" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69ccfcf1b5210036050bc5f1/Local_government_reorganisation_advisory_group_meeting_summary_18_March_2026.pdf</t>
+        </is>
+      </c>
+      <c r="J162" s="43" t="inlineStr"/>
+      <c r="K162" s="44" t="inlineStr"/>
+      <c r="L162" s="44" t="inlineStr">
+        <is>
+          <t>3e06834ec6a43ab6c7fec9c70e0cf656</t>
+        </is>
+      </c>
+      <c r="M162" s="44" t="inlineStr"/>
+    </row>
+    <row r="163" ht="40" customHeight="1" s="28">
+      <c r="A163" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B163" s="46" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation (LGR) Advisory Group 16 April 2026</t>
+        </is>
+      </c>
+      <c r="C163" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D163" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E163" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F163" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G163" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H163" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I163" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69e8ca77d36883a64473b838/20260416_LGRAG_April_Meeting_Short_Summary_.pdf</t>
+        </is>
+      </c>
+      <c r="J163" s="45" t="inlineStr"/>
+      <c r="K163" s="46" t="inlineStr"/>
+      <c r="L163" s="46" t="inlineStr">
+        <is>
+          <t>9704d74351bd5e684f579fb559388c20</t>
+        </is>
+      </c>
+      <c r="M163" s="46" t="inlineStr"/>
+    </row>
+    <row r="164" ht="40" customHeight="1" s="28">
+      <c r="A164" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B164" s="44" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation (LGR) Advisory Group 12 May 2026</t>
+        </is>
+      </c>
+      <c r="C164" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D164" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E164" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F164" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G164" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H164" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I164" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a0c3c7afcae986635db919b/LGRAG_May_Meeting_Short_Summary.pdf</t>
+        </is>
+      </c>
+      <c r="J164" s="43" t="inlineStr"/>
+      <c r="K164" s="44" t="inlineStr"/>
+      <c r="L164" s="44" t="inlineStr">
+        <is>
+          <t>9e825e676176ab3df7c2241d05e6708b</t>
+        </is>
+      </c>
+      <c r="M164" s="44" t="inlineStr"/>
+    </row>
+    <row r="165" ht="40" customHeight="1" s="28">
+      <c r="A165" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B165" s="46" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation (LGR) Advisory Group 11 June 2026</t>
+        </is>
+      </c>
+      <c r="C165" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D165" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E165" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F165" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G165" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H165" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I165" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a621cbce2d191f0bc8b6de6/LGRAG_June_Meeting_Short_Summary.pdf</t>
+        </is>
+      </c>
+      <c r="J165" s="45" t="inlineStr"/>
+      <c r="K165" s="46" t="inlineStr"/>
+      <c r="L165" s="46" t="inlineStr">
+        <is>
+          <t>f5b78258b271ad80e9922201c9792676</t>
+        </is>
+      </c>
+      <c r="M165" s="46" t="inlineStr"/>
+    </row>
+    <row r="166" ht="40" customHeight="1" s="28">
+      <c r="A166" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B166" s="44" t="inlineStr">
+        <is>
+          <t>Local Government Reorganisation (LGR) Advisory Group 23 July 2026</t>
+        </is>
+      </c>
+      <c r="C166" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D166" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E166" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F166" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G166" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H166" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I166" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a71bbe9dc689ac736a4766e/Local_government_reorganisation_advisory_group_meeting_summary_23_July_2026.pdf</t>
+        </is>
+      </c>
+      <c r="J166" s="43" t="inlineStr"/>
+      <c r="K166" s="44" t="inlineStr"/>
+      <c r="L166" s="44" t="inlineStr">
+        <is>
+          <t>b5a1bd87d323af69c2f074e01e1ae997</t>
+        </is>
+      </c>
+      <c r="M166" s="44" t="inlineStr"/>
+    </row>
+    <row r="167" ht="40" customHeight="1" s="28">
+      <c r="A167" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B167" s="46" t="inlineStr">
+        <is>
+          <t>Proposals for local government reorganisation in Nottinghamshire and Nottingham</t>
+        </is>
+      </c>
+      <c r="C167" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D167" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E167" s="45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="F167" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G167" s="46" t="inlineStr">
+        <is>
+          <t>Local, Transition</t>
+        </is>
+      </c>
+      <c r="H167" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I167" s="46" t="inlineStr">
+        <is>
+          <t>/government/consultations/local-government-reorganisation-in-nottinghamshire-and-nottingham/proposals-for-local-government-reorganisation-in-nottinghamshire-and-nottingham</t>
+        </is>
+      </c>
+      <c r="J167" s="45" t="inlineStr"/>
+      <c r="K167" s="46" t="inlineStr"/>
+      <c r="L167" s="46" t="inlineStr">
+        <is>
+          <t>1bc824c674f2b76bbd6ba50f18b5f21e</t>
+        </is>
+      </c>
+      <c r="M167" s="46" t="inlineStr"/>
+    </row>
+    <row r="168" ht="40" customHeight="1" s="28">
+      <c r="A168" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B168" s="44" t="inlineStr">
+        <is>
+          <t>Nottinghamshire and Nottingham: Summary and analysis of consultation responses</t>
+        </is>
+      </c>
+      <c r="C168" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D168" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E168" s="43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="F168" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G168" s="44" t="inlineStr">
+        <is>
+          <t>Local, Transition</t>
+        </is>
+      </c>
+      <c r="H168" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I168" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a60a25534dfb74772f96d06/Nottinghamshire_and_Nottingham_-_Summary_and_analysis_of_consultation_responses.pdf</t>
+        </is>
+      </c>
+      <c r="J168" s="43" t="inlineStr"/>
+      <c r="K168" s="44" t="inlineStr"/>
+      <c r="L168" s="44" t="inlineStr">
+        <is>
+          <t>e221487734bf2a83726fb1c13475f6eb</t>
+        </is>
+      </c>
+      <c r="M168" s="44" t="inlineStr"/>
+    </row>
+    <row r="169" ht="40" customHeight="1" s="28">
+      <c r="A169" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B169" s="46" t="inlineStr">
+        <is>
+          <t>Local government reorganisation: implementation letter to Nottinghamshire and Nottingham chief executives</t>
+        </is>
+      </c>
+      <c r="C169" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D169" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E169" s="45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F169" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G169" s="46" t="inlineStr">
+        <is>
+          <t>Local, Transition</t>
+        </is>
+      </c>
+      <c r="H169" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I169" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a6a10ada95350305084f78b/Local_government_reorganisation_-_implementation_letter_to_Nottinghamshire_and_Nottingham_chief_executives.pdf</t>
+        </is>
+      </c>
+      <c r="J169" s="45" t="inlineStr"/>
+      <c r="K169" s="46" t="inlineStr"/>
+      <c r="L169" s="46" t="inlineStr">
+        <is>
+          <t>38f9b366fa9fcb3b82d7b0f9a3d54865</t>
+        </is>
+      </c>
+      <c r="M169" s="46" t="inlineStr"/>
+    </row>
+    <row r="170" ht="40" customHeight="1" s="28">
+      <c r="A170" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B170" s="44" t="inlineStr">
+        <is>
+          <t>Letter to Council Leaders</t>
+        </is>
+      </c>
+      <c r="C170" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D170" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E170" s="43" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="F170" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G170" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H170" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I170" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69848c0f2df808759a7bd712/Letter_to_Council_Leaders_5_February_2026.pdf</t>
+        </is>
+      </c>
+      <c r="J170" s="43" t="inlineStr"/>
+      <c r="K170" s="44" t="inlineStr"/>
+      <c r="L170" s="44" t="inlineStr">
+        <is>
+          <t>b8613cbf9ef267df427e650bf47b9cbd</t>
+        </is>
+      </c>
+      <c r="M170" s="44" t="inlineStr"/>
+    </row>
+    <row r="171" ht="40" customHeight="1" s="28">
+      <c r="A171" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B171" s="46" t="inlineStr">
+        <is>
+          <t>Local Audit Transition Plan</t>
+        </is>
+      </c>
+      <c r="C171" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D171" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E171" s="45" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="F171" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G171" s="46" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="H171" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I171" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6926f871345e31ab14ecf524/Local_Audit_Transition_Plan.pdf</t>
+        </is>
+      </c>
+      <c r="J171" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K171" s="46" t="inlineStr">
+        <is>
+          <t>REVIEWED: MHCLG, Nov 2025. Annex A carries the LAO milestone timeline. Corrects OB-A10 — PSAA contracts with audit firms extended to 2030, not 2027/28. Auditor appointment and contracting duties transfer to the LAO Spring 2027. Confirms the statutory audit committee requirement behind OB-A13 and the SoS power to issue statutory guidance behind A-029.</t>
+        </is>
+      </c>
+      <c r="L171" s="46" t="inlineStr">
+        <is>
+          <t>ec93a5ad87c1fcbe3dfba567356b9f19</t>
+        </is>
+      </c>
+      <c r="M171" s="46" t="inlineStr"/>
+    </row>
+    <row r="172" ht="40" customHeight="1" s="28">
+      <c r="A172" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B172" s="44" t="inlineStr">
+        <is>
+          <t>Ministerial letter to audit firms</t>
+        </is>
+      </c>
+      <c r="C172" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D172" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E172" s="43" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="F172" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G172" s="44" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="H172" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I172" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/692992bf9c1eda2cdf03429c/Ministerial_letter_to_local_audit_firms.pdf</t>
+        </is>
+      </c>
+      <c r="J172" s="43" t="inlineStr"/>
+      <c r="K172" s="44" t="inlineStr"/>
+      <c r="L172" s="44" t="inlineStr">
+        <is>
+          <t>4b5a932c3b2d0c295d0e28fb608b6a10</t>
+        </is>
+      </c>
+      <c r="M172" s="44" t="inlineStr"/>
+    </row>
+    <row r="173" ht="40" customHeight="1" s="28">
+      <c r="A173" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B173" s="46" t="inlineStr">
+        <is>
+          <t>Ministerial letter to local bodies</t>
+        </is>
+      </c>
+      <c r="C173" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D173" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E173" s="45" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="F173" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G173" s="46" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="H173" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I173" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/692992e6a245b0985f034280/Ministerial_letter_to_local_bodies.pdf</t>
+        </is>
+      </c>
+      <c r="J173" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K173" s="46" t="inlineStr">
+        <is>
+          <t>REVIEWED: Alison McGovern MP to Chief Executives, CFOs and Leaders, 27 Nov 2025. Asks authorities to permit their auditor to share the Auditor Annual Report and ISA 260 with MHCLG by 31 Mar 2026, and a capacity assessment by end Jul 2026 — BOTH DATES NOW PASSED, needs a retrospective check that NCC responded. Backstop for clearing disclaimers is 30 Nov 2028. No further build-back grant in 2025/26.</t>
+        </is>
+      </c>
+      <c r="L173" s="46" t="inlineStr">
+        <is>
+          <t>2c4d9bf5ca20effcf72f58d6dd35b446</t>
+        </is>
+      </c>
+      <c r="M173" s="46" t="inlineStr"/>
+    </row>
+    <row r="174" ht="40" customHeight="1" s="28">
+      <c r="A174" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B174" s="44" t="inlineStr">
+        <is>
+          <t>Devolution Framework Explainer: Established Mayoral Strategic Authorities</t>
+        </is>
+      </c>
+      <c r="C174" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D174" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E174" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F174" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G174" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H174" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I174" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a26d62c8e85b4e5346ac0e2/Devolution_Framework_Explainer_-_Established_Mayoral_Strategic_Authorities.pdf</t>
+        </is>
+      </c>
+      <c r="J174" s="43" t="inlineStr"/>
+      <c r="K174" s="44" t="inlineStr"/>
+      <c r="L174" s="44" t="inlineStr">
+        <is>
+          <t>77f308678d96d12c59d3c6de5aee6058</t>
+        </is>
+      </c>
+      <c r="M174" s="44" t="inlineStr"/>
+    </row>
+    <row r="175" ht="40" customHeight="1" s="28">
+      <c r="A175" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B175" s="46" t="inlineStr">
+        <is>
+          <t>Devolution Framework Explainer: Mayoral Strategic Authorities</t>
+        </is>
+      </c>
+      <c r="C175" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D175" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E175" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F175" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G175" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H175" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I175" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a26d63b56960b0542c0b1bf/Devolution_Framework_Explainer_-_Mayoral_Strategic_Authorities.pdf</t>
+        </is>
+      </c>
+      <c r="J175" s="45" t="inlineStr"/>
+      <c r="K175" s="46" t="inlineStr"/>
+      <c r="L175" s="46" t="inlineStr">
+        <is>
+          <t>e949d04c576c4e340e3aa3380dfb1bf6</t>
+        </is>
+      </c>
+      <c r="M175" s="46" t="inlineStr"/>
+    </row>
+    <row r="176" ht="40" customHeight="1" s="28">
+      <c r="A176" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B176" s="44" t="inlineStr">
+        <is>
+          <t>Devolution Framework Explainer: Non-Mayoral Foundation Strategic Authorities</t>
+        </is>
+      </c>
+      <c r="C176" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D176" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E176" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F176" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G176" s="44" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H176" s="44" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I176" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a26d6498e85b4e5346ac0e3/Devolution_Framework_Explainer_-_Non-Mayoral_Foundation_Strategic_Authorities.pdf</t>
+        </is>
+      </c>
+      <c r="J176" s="43" t="inlineStr"/>
+      <c r="K176" s="44" t="inlineStr"/>
+      <c r="L176" s="44" t="inlineStr">
+        <is>
+          <t>63ea6abaf72e003caaa30e6bc86885dc</t>
+        </is>
+      </c>
+      <c r="M176" s="44" t="inlineStr"/>
+    </row>
+    <row r="177" ht="40" customHeight="1" s="28">
+      <c r="A177" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B177" s="46" t="inlineStr">
+        <is>
+          <t>Devolution Framework Explainer: Single Local Authority Foundation Strategic Authorities</t>
+        </is>
+      </c>
+      <c r="C177" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D177" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E177" s="45" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F177" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G177" s="46" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="H177" s="46" t="inlineStr">
+        <is>
+          <t>LGR Transition</t>
+        </is>
+      </c>
+      <c r="I177" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a26d657f56856fd11c0b19a/Devolution_Framework_Explainer_-_Single_Local_Authority_Foundation_Strategic_Authorities.pdf</t>
+        </is>
+      </c>
+      <c r="J177" s="45" t="inlineStr"/>
+      <c r="K177" s="46" t="inlineStr"/>
+      <c r="L177" s="46" t="inlineStr">
+        <is>
+          <t>52d602a87f08289fc5d853450f09deb5</t>
+        </is>
+      </c>
+      <c r="M177" s="46" t="inlineStr"/>
+    </row>
+    <row r="178" ht="40" customHeight="1" s="28">
+      <c r="A178" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B178" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Letter to Council Leader (15 July 2026)</t>
+        </is>
+      </c>
+      <c r="C178" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D178" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E178" s="43" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F178" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G178" s="44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H178" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I178" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a5759d19e631544544136cd/Nottingham_Minister_letter_to_Leader_of_the_Council_-_July_2026.pdf</t>
+        </is>
+      </c>
+      <c r="J178" s="43" t="inlineStr"/>
+      <c r="K178" s="44" t="inlineStr"/>
+      <c r="L178" s="44" t="inlineStr">
+        <is>
+          <t>7a5f34b199f0d96f9b51d9efcd859604</t>
+        </is>
+      </c>
+      <c r="M178" s="44" t="inlineStr"/>
+    </row>
+    <row r="179" ht="40" customHeight="1" s="28">
+      <c r="A179" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B179" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Ministerial Envoy appointment letter (15 July 2026)</t>
+        </is>
+      </c>
+      <c r="C179" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D179" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E179" s="45" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F179" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G179" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H179" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I179" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a574b882cbe5d1c179a6500/Sir_Steve_Houghton_Nottingham_appointment_letter_-_July_2026.pdf</t>
+        </is>
+      </c>
+      <c r="J179" s="45" t="inlineStr"/>
+      <c r="K179" s="46" t="inlineStr"/>
+      <c r="L179" s="46" t="inlineStr">
+        <is>
+          <t>2a0b875692191cb25f4eeda0d92f644e</t>
+        </is>
+      </c>
+      <c r="M179" s="46" t="inlineStr"/>
+    </row>
+    <row r="180" ht="40" customHeight="1" s="28">
+      <c r="A180" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B180" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Letter to Chief Executive (24 March 2026)</t>
+        </is>
+      </c>
+      <c r="C180" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D180" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E180" s="43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="F180" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G180" s="44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H180" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I180" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69c14cedbb0dfe55b83e4ba4/Nottingham_James_Blythe_Letter_to_Chief_Executive.pdf</t>
+        </is>
+      </c>
+      <c r="J180" s="43" t="inlineStr"/>
+      <c r="K180" s="44" t="inlineStr"/>
+      <c r="L180" s="44" t="inlineStr">
+        <is>
+          <t>8f1247a4f902928d0ea99043bb50d75d</t>
+        </is>
+      </c>
+      <c r="M180" s="44" t="inlineStr"/>
+    </row>
+    <row r="181" ht="40" customHeight="1" s="28">
+      <c r="A181" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B181" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Ministerial Envoy appointment letter</t>
+        </is>
+      </c>
+      <c r="C181" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D181" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E181" s="45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="F181" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G181" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H181" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I181" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69c14b1313101e9908704a8a/James_Blythe_Appointment_Letter_to_Sharon_Kemp.pdf</t>
+        </is>
+      </c>
+      <c r="J181" s="45" t="inlineStr"/>
+      <c r="K181" s="46" t="inlineStr"/>
+      <c r="L181" s="46" t="inlineStr">
+        <is>
+          <t>9e7e04afa0f983c1a329b728d25fe631</t>
+        </is>
+      </c>
+      <c r="M181" s="46" t="inlineStr"/>
+    </row>
+    <row r="182" ht="40" customHeight="1" s="28">
+      <c r="A182" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B182" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Letter to former Commissioners (24 March 2026)</t>
+        </is>
+      </c>
+      <c r="C182" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D182" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E182" s="43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="F182" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G182" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H182" s="44" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I182" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69c147fa13101e9908704a86/Minister_Letter_to_Notts_Commissioners.pdf</t>
+        </is>
+      </c>
+      <c r="J182" s="43" t="inlineStr"/>
+      <c r="K182" s="44" t="inlineStr"/>
+      <c r="L182" s="44" t="inlineStr">
+        <is>
+          <t>3aed4ba5a6cae16a7bdc7ca1fc2d756f</t>
+        </is>
+      </c>
+      <c r="M182" s="44" t="inlineStr"/>
+    </row>
+    <row r="183" ht="40" customHeight="1" s="28">
+      <c r="A183" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B183" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Directions made under the Local Government Act 1999 (24 March 2026)</t>
+        </is>
+      </c>
+      <c r="C183" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D183" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E183" s="45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="F183" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G183" s="46" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H183" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I183" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69c1756913101e9908704ada/Nottingham_Directions.pdf</t>
+        </is>
+      </c>
+      <c r="J183" s="45" t="inlineStr"/>
+      <c r="K183" s="46" t="inlineStr"/>
+      <c r="L183" s="46" t="inlineStr">
+        <is>
+          <t>745a507f92aa4f20356c24d9fddbbcec</t>
+        </is>
+      </c>
+      <c r="M183" s="46" t="inlineStr"/>
+    </row>
+    <row r="184" ht="40" customHeight="1" s="28">
+      <c r="A184" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B184" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Explanatory Memorandum (24 March 2026)</t>
+        </is>
+      </c>
+      <c r="C184" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D184" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E184" s="43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="F184" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G184" s="44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H184" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I184" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69c174e813101e9908704ad9/Nottingham_Explanatory_Memorandum.pdf</t>
+        </is>
+      </c>
+      <c r="J184" s="43" t="inlineStr"/>
+      <c r="K184" s="44" t="inlineStr"/>
+      <c r="L184" s="44" t="inlineStr">
+        <is>
+          <t>c384fde51b1381f329d636a0e05ba995</t>
+        </is>
+      </c>
+      <c r="M184" s="44" t="inlineStr"/>
+    </row>
+    <row r="185" ht="40" customHeight="1" s="28">
+      <c r="A185" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B185" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Representation (24 March 2026)</t>
+        </is>
+      </c>
+      <c r="C185" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D185" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E185" s="45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="F185" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G185" s="46" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H185" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I185" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/69c14e22bb0dfe55b83e4bab/Nottingham_City_Council_Representation_260211.pdf</t>
+        </is>
+      </c>
+      <c r="J185" s="45" t="inlineStr"/>
+      <c r="K185" s="46" t="inlineStr"/>
+      <c r="L185" s="46" t="inlineStr">
+        <is>
+          <t>c060c252e02f39bab3c0aedae03b29fa</t>
+        </is>
+      </c>
+      <c r="M185" s="46" t="inlineStr"/>
+    </row>
+    <row r="186" ht="40" customHeight="1" s="28">
+      <c r="A186" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B186" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Letter to the Chief Executive (4 February 2026)</t>
+        </is>
+      </c>
+      <c r="C186" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D186" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E186" s="43" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="F186" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G186" s="44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H186" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I186" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6981aa11f0e5cf1ed2612e50/Letter_to_Nottingham_Chief_Executive.pdf</t>
+        </is>
+      </c>
+      <c r="J186" s="43" t="inlineStr"/>
+      <c r="K186" s="44" t="inlineStr"/>
+      <c r="L186" s="44" t="inlineStr">
+        <is>
+          <t>8b487dcc8f1b251da1feaf064d9ae38d</t>
+        </is>
+      </c>
+      <c r="M186" s="44" t="inlineStr"/>
+    </row>
+    <row r="187" ht="40" customHeight="1" s="28">
+      <c r="A187" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B187" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Ministerial response to the Commissioners’ fourth report</t>
+        </is>
+      </c>
+      <c r="C187" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D187" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E187" s="45" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="F187" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G187" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H187" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I187" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6981a8e23915f71236580144/Minister_Response_to_Commissioners_Report.pdf</t>
+        </is>
+      </c>
+      <c r="J187" s="45" t="inlineStr"/>
+      <c r="K187" s="46" t="inlineStr"/>
+      <c r="L187" s="46" t="inlineStr">
+        <is>
+          <t>eea4d6fa6a936f82df1a43a3db214be6</t>
+        </is>
+      </c>
+      <c r="M187" s="46" t="inlineStr"/>
+    </row>
+    <row r="188" ht="40" customHeight="1" s="28">
+      <c r="A188" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B188" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Commissioners’ fourth report</t>
+        </is>
+      </c>
+      <c r="C188" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D188" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E188" s="43" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="F188" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G188" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H188" s="44" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I188" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6981a50584f2153b11245387/Fourth_Report_Nottingham_City_Council_Commissioners__-_5_Dec_2025.pdf</t>
+        </is>
+      </c>
+      <c r="J188" s="43" t="inlineStr"/>
+      <c r="K188" s="44" t="inlineStr"/>
+      <c r="L188" s="44" t="inlineStr">
+        <is>
+          <t>e1b0a957888f453ec83abfcd05e8cf74</t>
+        </is>
+      </c>
+      <c r="M188" s="44" t="inlineStr"/>
+    </row>
+    <row r="189" ht="40" customHeight="1" s="28">
+      <c r="A189" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B189" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Explanatory Memorandum (updated 21 November 2025)</t>
+        </is>
+      </c>
+      <c r="C189" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D189" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E189" s="45" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="F189" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G189" s="46" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H189" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I189" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/691da521d140bbbaa59a2a0a/Updated_Explanatory_Memorandum_-_Nottingham.pdf</t>
+        </is>
+      </c>
+      <c r="J189" s="45" t="inlineStr"/>
+      <c r="K189" s="46" t="inlineStr"/>
+      <c r="L189" s="46" t="inlineStr">
+        <is>
+          <t>137eb83be5e8155978a7591feec4fc7b</t>
+        </is>
+      </c>
+      <c r="M189" s="46" t="inlineStr"/>
+    </row>
+    <row r="190" ht="40" customHeight="1" s="28">
+      <c r="A190" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B190" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Lead Commissioner appointment letter (Sharon Kemp)</t>
+        </is>
+      </c>
+      <c r="C190" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D190" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E190" s="43" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="F190" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G190" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H190" s="44" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I190" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/691da2e4e39a085bda43ef63/Sharon_Kemp_Nottingham_Appointment_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="J190" s="43" t="inlineStr"/>
+      <c r="K190" s="44" t="inlineStr"/>
+      <c r="L190" s="44" t="inlineStr">
+        <is>
+          <t>8e2cce2075f077f6175a910e08201bbc</t>
+        </is>
+      </c>
+      <c r="M190" s="44" t="inlineStr"/>
+    </row>
+    <row r="191" ht="40" customHeight="1" s="28">
+      <c r="A191" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B191" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Commissioner appointment letter (Tony McArdle)</t>
+        </is>
+      </c>
+      <c r="C191" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D191" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E191" s="45" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="F191" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G191" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H191" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I191" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/691da36a513046b952c50044/Tony_McArdle_Nottingham_Appointment_Letter.pdf</t>
+        </is>
+      </c>
+      <c r="J191" s="45" t="inlineStr"/>
+      <c r="K191" s="46" t="inlineStr"/>
+      <c r="L191" s="46" t="inlineStr">
+        <is>
+          <t>09e9a5aa3a1f1401eabe7427cc9b47a1</t>
+        </is>
+      </c>
+      <c r="M191" s="46" t="inlineStr"/>
+    </row>
+    <row r="192" ht="40" customHeight="1" s="28">
+      <c r="A192" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B192" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Ministerial response to the Commissioners’ third report</t>
+        </is>
+      </c>
+      <c r="C192" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D192" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E192" s="43" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="F192" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G192" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H192" s="44" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I192" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/691da11b0dcbf6343e9a29f9/Minister_McGovern_Response_to_Nottingham_Commissioners.pdf</t>
+        </is>
+      </c>
+      <c r="J192" s="43" t="inlineStr"/>
+      <c r="K192" s="44" t="inlineStr"/>
+      <c r="L192" s="44" t="inlineStr">
+        <is>
+          <t>2fba4d086038d9207621361c8eec0240</t>
+        </is>
+      </c>
+      <c r="M192" s="44" t="inlineStr"/>
+    </row>
+    <row r="193" ht="40" customHeight="1" s="28">
+      <c r="A193" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B193" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Commissioners’ third report</t>
+        </is>
+      </c>
+      <c r="C193" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D193" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E193" s="45" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="F193" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G193" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H193" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I193" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/691d9f760dcbf6343e9a29ec/Nottingham_Commissioners__third_report.pdf</t>
+        </is>
+      </c>
+      <c r="J193" s="45" t="inlineStr"/>
+      <c r="K193" s="46" t="inlineStr"/>
+      <c r="L193" s="46" t="inlineStr">
+        <is>
+          <t>f6b056283dee623a67765d5057e64e29</t>
+        </is>
+      </c>
+      <c r="M193" s="46" t="inlineStr"/>
+    </row>
+    <row r="194" ht="40" customHeight="1" s="28">
+      <c r="A194" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B194" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Ministerial response to the Commissioners’ second report</t>
+        </is>
+      </c>
+      <c r="C194" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D194" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E194" s="43" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="F194" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G194" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H194" s="44" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I194" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/681b71ad275cb67b18d87031/Nottingham_-_BT_Letter_to_Commissioners.pdf</t>
+        </is>
+      </c>
+      <c r="J194" s="43" t="inlineStr"/>
+      <c r="K194" s="44" t="inlineStr"/>
+      <c r="L194" s="44" t="inlineStr">
+        <is>
+          <t>622a9cd39d604a8a09d1df3803e58987</t>
+        </is>
+      </c>
+      <c r="M194" s="44" t="inlineStr"/>
+    </row>
+    <row r="195" ht="40" customHeight="1" s="28">
+      <c r="A195" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B195" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Commissioners’ second report</t>
+        </is>
+      </c>
+      <c r="C195" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D195" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E195" s="45" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="F195" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G195" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H195" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I195" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/681b6fba3f1c73824ee3e538/Nottingham_Commissioners_Second_Report_March_2025.pdf</t>
+        </is>
+      </c>
+      <c r="J195" s="45" t="inlineStr"/>
+      <c r="K195" s="46" t="inlineStr"/>
+      <c r="L195" s="46" t="inlineStr">
+        <is>
+          <t>d0c4aa38cacc84d33879e8a21c14a906</t>
+        </is>
+      </c>
+      <c r="M195" s="46" t="inlineStr"/>
+    </row>
+    <row r="196" ht="40" customHeight="1" s="28">
+      <c r="A196" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B196" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Exceptional Financial Support request 2025-26</t>
+        </is>
+      </c>
+      <c r="C196" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D196" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E196" s="43" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="F196" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G196" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H196" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I196" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/67cae216ade26736dbfa002b/Nottingham_City_Council_-_Exceptional_Financial_Support_request_2025-26.pdf</t>
+        </is>
+      </c>
+      <c r="J196" s="43" t="inlineStr"/>
+      <c r="K196" s="44" t="inlineStr"/>
+      <c r="L196" s="44" t="inlineStr">
+        <is>
+          <t>5df9c5bb373b451c02a462f88155b573</t>
+        </is>
+      </c>
+      <c r="M196" s="44" t="inlineStr"/>
+    </row>
+    <row r="197" ht="40" customHeight="1" s="28">
+      <c r="A197" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B197" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Ministerial response to Commissioners’ first report</t>
+        </is>
+      </c>
+      <c r="C197" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D197" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E197" s="45" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="F197" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G197" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H197" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I197" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/675962be79e8a9792b711117/Ministerial_Response_to_Nottingham_Commissioners__first_report.pdf</t>
+        </is>
+      </c>
+      <c r="J197" s="45" t="inlineStr"/>
+      <c r="K197" s="46" t="inlineStr"/>
+      <c r="L197" s="46" t="inlineStr">
+        <is>
+          <t>948914f0c28af5425e348ea10c4efb59</t>
+        </is>
+      </c>
+      <c r="M197" s="46" t="inlineStr"/>
+    </row>
+    <row r="198" ht="40" customHeight="1" s="28">
+      <c r="A198" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B198" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Commissioners' first report</t>
+        </is>
+      </c>
+      <c r="C198" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D198" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E198" s="43" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="F198" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G198" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H198" s="44" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I198" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/675961bf79e8a9792b711115/Nottingham_Commissioners__first_report.pdf</t>
+        </is>
+      </c>
+      <c r="J198" s="43" t="inlineStr"/>
+      <c r="K198" s="44" t="inlineStr"/>
+      <c r="L198" s="44" t="inlineStr">
+        <is>
+          <t>3ff8a559cfc576c231c3341457cc3e3b</t>
+        </is>
+      </c>
+      <c r="M198" s="44" t="inlineStr"/>
+    </row>
+    <row r="199" ht="40" customHeight="1" s="28">
+      <c r="A199" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B199" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council Improvement and Assurance Board: final report</t>
+        </is>
+      </c>
+      <c r="C199" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D199" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E199" s="45" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="F199" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G199" s="46" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H199" s="46" t="inlineStr">
+        <is>
+          <t>Internal Controls</t>
+        </is>
+      </c>
+      <c r="I199" s="46" t="inlineStr">
+        <is>
+          <t>/government/publications/nottingham-city-council-improvement-and-assurance-board-final-report/nottingham-city-council-improvement-and-assurance-board-final-report</t>
+        </is>
+      </c>
+      <c r="J199" s="45" t="inlineStr"/>
+      <c r="K199" s="46" t="inlineStr"/>
+      <c r="L199" s="46" t="inlineStr">
+        <is>
+          <t>df0a933e5e3aa76e7ff8faa75ddab56e</t>
+        </is>
+      </c>
+      <c r="M199" s="46" t="inlineStr"/>
+    </row>
+    <row r="200" ht="40" customHeight="1" s="28">
+      <c r="A200" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B200" s="44" t="inlineStr">
+        <is>
+          <t>​​Nottingham City Council: Explanatory Memorandum (updated 11 April 2024)​</t>
+        </is>
+      </c>
+      <c r="C200" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D200" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E200" s="43" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="F200" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G200" s="44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H200" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I200" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6616bd3156df202ca4ac05fc/NCC_Revised_Explanatory_Memorandum.pdf</t>
+        </is>
+      </c>
+      <c r="J200" s="43" t="inlineStr"/>
+      <c r="K200" s="44" t="inlineStr"/>
+      <c r="L200" s="44" t="inlineStr">
+        <is>
+          <t>7ccabb3c8021cc368da2cbd9d2b4340d</t>
+        </is>
+      </c>
+      <c r="M200" s="44" t="inlineStr"/>
+    </row>
+    <row r="201" ht="40" customHeight="1" s="28">
+      <c r="A201" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B201" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Lead Commissioner appointment letter (Tony McArdle)</t>
+        </is>
+      </c>
+      <c r="C201" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D201" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E201" s="45" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="F201" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G201" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H201" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I201" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65d716c3188d77001103887d/Nottingham_City_Council_Lead_Commissioner_appointment_letter__Tony_McArdle_.pdf</t>
+        </is>
+      </c>
+      <c r="J201" s="45" t="inlineStr"/>
+      <c r="K201" s="46" t="inlineStr"/>
+      <c r="L201" s="46" t="inlineStr">
+        <is>
+          <t>19ea7843198673d8c167be5949be06c0</t>
+        </is>
+      </c>
+      <c r="M201" s="46" t="inlineStr"/>
+    </row>
+    <row r="202" ht="40" customHeight="1" s="28">
+      <c r="A202" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B202" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Commissioner appointment letter (Margaret Lee)</t>
+        </is>
+      </c>
+      <c r="C202" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D202" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E202" s="43" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="F202" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G202" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H202" s="44" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I202" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65d7179b188d77a8d3038774/Nottingham_City_Council_Commissioner_appointment_letter__Margaret_Lee_.pdf</t>
+        </is>
+      </c>
+      <c r="J202" s="43" t="inlineStr"/>
+      <c r="K202" s="44" t="inlineStr"/>
+      <c r="L202" s="44" t="inlineStr">
+        <is>
+          <t>85630cbc0e7368b0d87f1000ee3afaa6</t>
+        </is>
+      </c>
+      <c r="M202" s="44" t="inlineStr"/>
+    </row>
+    <row r="203" ht="40" customHeight="1" s="28">
+      <c r="A203" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B203" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Commissioner appointment letter (Sharon Kemp)</t>
+        </is>
+      </c>
+      <c r="C203" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D203" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E203" s="45" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="F203" s="45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G203" s="46" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H203" s="46" t="inlineStr">
+        <is>
+          <t>Governance and Transparency</t>
+        </is>
+      </c>
+      <c r="I203" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6616b31a1a70cf4b92093246/NCC_Commissioner_Appointment_Letter_Sharon_Kemp.pdf</t>
+        </is>
+      </c>
+      <c r="J203" s="45" t="inlineStr"/>
+      <c r="K203" s="46" t="inlineStr"/>
+      <c r="L203" s="46" t="inlineStr">
+        <is>
+          <t>e7ca97105a4a5b9358a7c7b57168cb53</t>
+        </is>
+      </c>
+      <c r="M203" s="46" t="inlineStr"/>
+    </row>
+    <row r="204" ht="40" customHeight="1" s="28">
+      <c r="A204" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B204" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Exceptional Financial Support request 2024-25</t>
+        </is>
+      </c>
+      <c r="C204" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D204" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E204" s="43" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="F204" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G204" s="44" t="inlineStr">
+        <is>
+          <t>Local, Intervention</t>
+        </is>
+      </c>
+      <c r="H204" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I204" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65df5aeef1cab36b60fc4738/Exceptional_Financial_Support_Letter_-_Nottingham_City_Council_2024-25.pdf</t>
+        </is>
+      </c>
+      <c r="J204" s="43" t="inlineStr"/>
+      <c r="K204" s="44" t="inlineStr"/>
+      <c r="L204" s="44" t="inlineStr">
+        <is>
+          <t>30595b99ee22d46036f2e566020f7ad6</t>
+        </is>
+      </c>
+      <c r="M204" s="44" t="inlineStr"/>
+    </row>
+    <row r="205" ht="40" customHeight="1" s="28">
+      <c r="A205" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B205" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Letter to the Chief Executive (22 February 2024)</t>
+        </is>
+      </c>
+      <c r="C205" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D205" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E205" s="45" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="F205" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G205" s="46" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H205" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I205" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65d744ec54f1e7001a165885/Nottingham_City_Council_Letter_to_the_Chief_Executive__22_February_2024_.pdf</t>
+        </is>
+      </c>
+      <c r="J205" s="45" t="inlineStr"/>
+      <c r="K205" s="46" t="inlineStr"/>
+      <c r="L205" s="46" t="inlineStr">
+        <is>
+          <t>10a0bc76cde45b413d51f54ede47f880</t>
+        </is>
+      </c>
+      <c r="M205" s="46" t="inlineStr"/>
+    </row>
+    <row r="206" ht="40" customHeight="1" s="28">
+      <c r="A206" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B206" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Ministerial letter to Sir Tony Redmond (22 February 2024)</t>
+        </is>
+      </c>
+      <c r="C206" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D206" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E206" s="43" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="F206" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G206" s="44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H206" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I206" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65d71d7f2ab2b3e0f27595ad/Nottingham_City_Council_Ministerial_response_to_Sir_Tony_Redmond__22_February_2024_.pdf</t>
+        </is>
+      </c>
+      <c r="J206" s="43" t="inlineStr"/>
+      <c r="K206" s="44" t="inlineStr"/>
+      <c r="L206" s="44" t="inlineStr">
+        <is>
+          <t>1ab8bb28f82ff71064ebd6d3d60f432f</t>
+        </is>
+      </c>
+      <c r="M206" s="44" t="inlineStr"/>
+    </row>
+    <row r="207" ht="40" customHeight="1" s="28">
+      <c r="A207" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B207" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Directions made under the Local Government Act 1999 (22 February 2024)</t>
+        </is>
+      </c>
+      <c r="C207" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D207" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E207" s="45" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="F207" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G207" s="46" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H207" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I207" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65d713262197b200117fa80a/Nottingham_City_Council_Directions_made_under_the_Local_Government_Act_1999__22_February_2024_.pdf</t>
+        </is>
+      </c>
+      <c r="J207" s="45" t="inlineStr"/>
+      <c r="K207" s="46" t="inlineStr"/>
+      <c r="L207" s="46" t="inlineStr">
+        <is>
+          <t>9ddf0b01939c768e46e11a517a832ed2</t>
+        </is>
+      </c>
+      <c r="M207" s="46" t="inlineStr"/>
+    </row>
+    <row r="208" ht="40" customHeight="1" s="28">
+      <c r="A208" s="43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B208" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Explanatory Memorandum (22 February 2024)</t>
+        </is>
+      </c>
+      <c r="C208" s="44" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D208" s="44" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E208" s="43" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="F208" s="43" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G208" s="44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H208" s="44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I208" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65d713b6188d770011038878/Nottingham_City_Council_Explanatory_Memorandum__22_February_2024_.pdf</t>
+        </is>
+      </c>
+      <c r="J208" s="43" t="inlineStr"/>
+      <c r="K208" s="44" t="inlineStr"/>
+      <c r="L208" s="44" t="inlineStr">
+        <is>
+          <t>6c3a9937c1548e83108b1ada5c4e559a</t>
+        </is>
+      </c>
+      <c r="M208" s="44" t="inlineStr"/>
+    </row>
+    <row r="209" ht="40" customHeight="1" s="28">
+      <c r="A209" s="45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B209" s="46" t="inlineStr">
+        <is>
+          <t>Nottingham City Council: Representation (22 February 2024)</t>
+        </is>
+      </c>
+      <c r="C209" s="46" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="D209" s="46" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="E209" s="45" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="F209" s="45" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="G209" s="46" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H209" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I209" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65d72394188d77a8d303878c/Nottingham_City_Council_Representation__22_February_2024_.pdf</t>
+        </is>
+      </c>
+      <c r="J209" s="45" t="inlineStr"/>
+      <c r="K209" s="46" t="inlineStr"/>
+      <c r="L209" s="46" t="inlineStr">
+        <is>
+          <t>3ff2d1093161f0e8a2973d18e812185a</t>
+        </is>
+      </c>
+      <c r="M209" s="46" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M131"/>
+  <autoFilter ref="A1:M209"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>

--- a/AuditTracker.xlsx
+++ b/AuditTracker.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Intelligence'!$A$1:$M$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Obligations'!$A$1:$O$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Actions'!$A$1:$L$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidence Gaps'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Actions'!$A$1:$L$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidence Gaps'!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -633,6 +633,69 @@
     </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1571,29 +1634,29 @@
   <sheetData>
     <row r="1" ht="8" customHeight="1" s="28"/>
     <row r="2" ht="4" customHeight="1" s="28">
-      <c r="A2" s="117" t="n"/>
-      <c r="B2" s="117" t="n"/>
-      <c r="C2" s="117" t="n"/>
-      <c r="D2" s="117" t="n"/>
-      <c r="E2" s="117" t="n"/>
-      <c r="F2" s="117" t="n"/>
-      <c r="G2" s="117" t="n"/>
-      <c r="H2" s="117" t="n"/>
-      <c r="I2" s="117" t="n"/>
-      <c r="J2" s="117" t="n"/>
-      <c r="K2" s="117" t="n"/>
-      <c r="L2" s="117" t="n"/>
-      <c r="M2" s="117" t="n"/>
+      <c r="A2" s="138" t="n"/>
+      <c r="B2" s="138" t="n"/>
+      <c r="C2" s="138" t="n"/>
+      <c r="D2" s="138" t="n"/>
+      <c r="E2" s="138" t="n"/>
+      <c r="F2" s="138" t="n"/>
+      <c r="G2" s="138" t="n"/>
+      <c r="H2" s="138" t="n"/>
+      <c r="I2" s="138" t="n"/>
+      <c r="J2" s="138" t="n"/>
+      <c r="K2" s="138" t="n"/>
+      <c r="L2" s="138" t="n"/>
+      <c r="M2" s="138" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="28">
-      <c r="B3" s="118" t="inlineStr">
+      <c r="B3" s="139" t="inlineStr">
         <is>
           <t>NCC Audit Reform and LGR Obligations Tracker</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1" s="28">
-      <c r="B4" s="119" t="inlineStr">
+      <c r="B4" s="140" t="inlineStr">
         <is>
           <t>Live status snapshot  ·  Refreshed 04 August 2026</t>
         </is>
@@ -1601,42 +1664,42 @@
     </row>
     <row r="5" ht="12" customHeight="1" s="28"/>
     <row r="6" ht="6" customHeight="1" s="28">
-      <c r="B6" s="117" t="n"/>
-      <c r="E6" s="117" t="n"/>
-      <c r="H6" s="117" t="n"/>
-      <c r="K6" s="117" t="n"/>
+      <c r="B6" s="138" t="n"/>
+      <c r="E6" s="138" t="n"/>
+      <c r="H6" s="138" t="n"/>
+      <c r="K6" s="138" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1" s="28">
-      <c r="B7" s="120" t="n">
+      <c r="B7" s="141" t="n">
         <v>22</v>
       </c>
-      <c r="E7" s="121" t="n">
+      <c r="E7" s="142" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="122" t="n">
+      <c r="H7" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="122" t="n">
+      <c r="K7" s="143" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="28">
-      <c r="B8" s="123" t="inlineStr">
+      <c r="B8" s="144" t="inlineStr">
         <is>
           <t>OBLIGATIONS</t>
         </is>
       </c>
-      <c r="E8" s="124" t="inlineStr">
+      <c r="E8" s="145" t="inlineStr">
         <is>
           <t>OVERDUE</t>
         </is>
       </c>
-      <c r="H8" s="125" t="inlineStr">
+      <c r="H8" s="146" t="inlineStr">
         <is>
           <t>DUE IN 30 DAYS</t>
         </is>
       </c>
-      <c r="K8" s="125" t="inlineStr">
+      <c r="K8" s="146" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -1644,7 +1707,7 @@
     </row>
     <row r="9" ht="14" customHeight="1" s="28"/>
     <row r="10" ht="20" customHeight="1" s="28">
-      <c r="B10" s="126" t="inlineStr">
+      <c r="B10" s="147" t="inlineStr">
         <is>
           <t xml:space="preserve">  OBLIGATIONS OVERVIEW</t>
         </is>
@@ -1652,181 +1715,181 @@
     </row>
     <row r="11" ht="8" customHeight="1" s="28"/>
     <row r="12" ht="16" customHeight="1" s="28">
-      <c r="B12" s="127" t="inlineStr">
+      <c r="B12" s="148" t="inlineStr">
         <is>
           <t>Obligations by Status</t>
         </is>
       </c>
-      <c r="F12" s="127" t="inlineStr">
+      <c r="F12" s="148" t="inlineStr">
         <is>
           <t>Obligations by Risk</t>
         </is>
       </c>
-      <c r="J12" s="127" t="inlineStr">
+      <c r="J12" s="148" t="inlineStr">
         <is>
           <t>Obligations by Theme</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="28">
-      <c r="B13" s="128" t="inlineStr">
+      <c r="B13" s="149" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
       <c r="C13" s="60" t="n"/>
-      <c r="D13" s="129" t="inlineStr">
+      <c r="D13" s="150" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="F13" s="128" t="inlineStr">
+      <c r="F13" s="149" t="inlineStr">
         <is>
           <t>Risk Rating</t>
         </is>
       </c>
       <c r="G13" s="60" t="n"/>
-      <c r="H13" s="129" t="inlineStr">
+      <c r="H13" s="150" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="J13" s="128" t="inlineStr">
+      <c r="J13" s="149" t="inlineStr">
         <is>
           <t>Theme</t>
         </is>
       </c>
       <c r="K13" s="60" t="n"/>
-      <c r="L13" s="129" t="inlineStr">
+      <c r="L13" s="150" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="28">
-      <c r="B14" s="130" t="inlineStr">
+      <c r="B14" s="151" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
       <c r="C14" s="60" t="n"/>
-      <c r="D14" s="131" t="n">
+      <c r="D14" s="152" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="130" t="inlineStr">
+      <c r="F14" s="151" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="G14" s="60" t="n"/>
-      <c r="H14" s="131" t="n">
+      <c r="H14" s="152" t="n">
         <v>17</v>
       </c>
-      <c r="J14" s="130" t="inlineStr">
+      <c r="J14" s="151" t="inlineStr">
         <is>
           <t>Governance and Transparency</t>
         </is>
       </c>
       <c r="K14" s="60" t="n"/>
-      <c r="L14" s="131" t="n">
+      <c r="L14" s="152" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="28">
-      <c r="B15" s="132" t="inlineStr">
+      <c r="B15" s="153" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
       <c r="C15" s="60" t="n"/>
-      <c r="D15" s="133" t="n">
+      <c r="D15" s="154" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="132" t="inlineStr">
+      <c r="F15" s="153" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="60" t="n"/>
-      <c r="H15" s="133" t="n">
+      <c r="H15" s="154" t="n">
         <v>5</v>
       </c>
-      <c r="J15" s="132" t="inlineStr">
+      <c r="J15" s="153" t="inlineStr">
         <is>
           <t>LGR Transition</t>
         </is>
       </c>
       <c r="K15" s="60" t="n"/>
-      <c r="L15" s="133" t="n">
+      <c r="L15" s="154" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="28">
-      <c r="B16" s="130" t="inlineStr">
+      <c r="B16" s="151" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
       <c r="C16" s="60" t="n"/>
-      <c r="D16" s="131" t="n">
+      <c r="D16" s="152" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="130" t="inlineStr">
+      <c r="F16" s="151" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="G16" s="60" t="n"/>
-      <c r="H16" s="131" t="n">
+      <c r="H16" s="152" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="130" t="inlineStr">
+      <c r="J16" s="151" t="inlineStr">
         <is>
           <t>Financial Reporting</t>
         </is>
       </c>
       <c r="K16" s="60" t="n"/>
-      <c r="L16" s="131" t="n">
+      <c r="L16" s="152" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="28">
-      <c r="B17" s="132" t="inlineStr">
+      <c r="B17" s="153" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
       <c r="C17" s="60" t="n"/>
-      <c r="D17" s="133" t="n">
+      <c r="D17" s="154" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="132" t="inlineStr">
+      <c r="J17" s="153" t="inlineStr">
         <is>
           <t>Audit Procurement</t>
         </is>
       </c>
       <c r="K17" s="60" t="n"/>
-      <c r="L17" s="133" t="n">
+      <c r="L17" s="154" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="28">
-      <c r="B18" s="130" t="inlineStr">
+      <c r="B18" s="151" t="inlineStr">
         <is>
           <t>Ongoing</t>
         </is>
       </c>
       <c r="C18" s="60" t="n"/>
-      <c r="D18" s="131" t="n">
+      <c r="D18" s="152" t="n">
         <v>8</v>
       </c>
-      <c r="J18" s="130" t="inlineStr">
+      <c r="J18" s="151" t="inlineStr">
         <is>
           <t>Internal Controls</t>
         </is>
       </c>
       <c r="K18" s="60" t="n"/>
-      <c r="L18" s="131" t="n">
+      <c r="L18" s="152" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1850,7 +1913,7 @@
     <row r="36" ht="15" customHeight="1" s="28"/>
     <row r="37" ht="14" customHeight="1" s="28"/>
     <row r="38" ht="20" customHeight="1" s="28">
-      <c r="B38" s="126" t="inlineStr">
+      <c r="B38" s="147" t="inlineStr">
         <is>
           <t xml:space="preserve">  ACTIONS &amp; INTELLIGENCE FEED</t>
         </is>
@@ -1858,143 +1921,143 @@
     </row>
     <row r="39" ht="8" customHeight="1" s="28"/>
     <row r="40" ht="18" customHeight="1" s="28">
-      <c r="B40" s="128" t="inlineStr">
+      <c r="B40" s="149" t="inlineStr">
         <is>
           <t>Action Summary</t>
         </is>
       </c>
       <c r="C40" s="60" t="n"/>
-      <c r="D40" s="129" t="inlineStr">
+      <c r="D40" s="150" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="F40" s="128" t="inlineStr">
+      <c r="F40" s="149" t="inlineStr">
         <is>
           <t>Intelligence Feed</t>
         </is>
       </c>
       <c r="G40" s="60" t="n"/>
-      <c r="H40" s="129" t="inlineStr">
+      <c r="H40" s="150" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="28">
-      <c r="B41" s="130" t="inlineStr">
+      <c r="B41" s="151" t="inlineStr">
         <is>
           <t>Total actions</t>
         </is>
       </c>
       <c r="C41" s="60" t="n"/>
-      <c r="D41" s="131" t="n">
-        <v>32</v>
-      </c>
-      <c r="F41" s="130" t="inlineStr">
+      <c r="D41" s="152" t="n">
+        <v>34</v>
+      </c>
+      <c r="F41" s="151" t="inlineStr">
         <is>
           <t>Items captured</t>
         </is>
       </c>
       <c r="G41" s="60" t="n"/>
-      <c r="H41" s="131" t="n">
+      <c r="H41" s="152" t="n">
         <v>208</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="28">
-      <c r="B42" s="132" t="inlineStr">
+      <c r="B42" s="153" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
       <c r="C42" s="60" t="n"/>
-      <c r="D42" s="133" t="n">
+      <c r="D42" s="154" t="n">
         <v>10</v>
       </c>
-      <c r="F42" s="132" t="inlineStr">
+      <c r="F42" s="153" t="inlineStr">
         <is>
           <t>Flagged material</t>
         </is>
       </c>
       <c r="G42" s="60" t="n"/>
-      <c r="H42" s="133" t="n">
+      <c r="H42" s="154" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="28">
-      <c r="B43" s="130" t="inlineStr">
+      <c r="B43" s="151" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
       <c r="C43" s="60" t="n"/>
-      <c r="D43" s="131" t="n">
+      <c r="D43" s="152" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="130" t="inlineStr">
+      <c r="F43" s="151" t="inlineStr">
         <is>
           <t>Material (last 30 days)</t>
         </is>
       </c>
       <c r="G43" s="60" t="n"/>
-      <c r="H43" s="131" t="n">
+      <c r="H43" s="152" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="28">
-      <c r="B44" s="132" t="inlineStr">
+      <c r="B44" s="153" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
       <c r="C44" s="60" t="n"/>
-      <c r="D44" s="133" t="n">
+      <c r="D44" s="154" t="n">
         <v>7</v>
       </c>
-      <c r="F44" s="132" t="inlineStr">
+      <c r="F44" s="153" t="inlineStr">
         <is>
           <t>Awaiting review</t>
         </is>
       </c>
       <c r="G44" s="60" t="n"/>
-      <c r="H44" s="133" t="n">
+      <c r="H44" s="154" t="n">
         <v>134</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1" s="28">
-      <c r="B45" s="130" t="inlineStr">
+      <c r="B45" s="151" t="inlineStr">
         <is>
           <t>Avg. progress</t>
         </is>
       </c>
       <c r="C45" s="60" t="n"/>
-      <c r="D45" s="131" t="inlineStr">
-        <is>
-          <t>8%</t>
+      <c r="D45" s="152" t="inlineStr">
+        <is>
+          <t>7%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1" s="28">
-      <c r="B46" s="132" t="inlineStr">
+      <c r="B46" s="153" t="inlineStr">
         <is>
           <t>Evidence coverage</t>
         </is>
       </c>
       <c r="C46" s="60" t="n"/>
-      <c r="D46" s="133" t="inlineStr">
-        <is>
-          <t>22% (7/32)</t>
+      <c r="D46" s="154" t="inlineStr">
+        <is>
+          <t>29% (10/34)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1" s="28">
-      <c r="B47" s="130" t="inlineStr">
+      <c r="B47" s="151" t="inlineStr">
         <is>
           <t>Evidence at completion</t>
         </is>
       </c>
       <c r="C47" s="60" t="n"/>
-      <c r="D47" s="131" t="inlineStr">
+      <c r="D47" s="152" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2002,7 +2065,7 @@
     </row>
     <row r="48" ht="14" customHeight="1" s="28"/>
     <row r="49" ht="20" customHeight="1" s="28">
-      <c r="B49" s="126" t="inlineStr">
+      <c r="B49" s="147" t="inlineStr">
         <is>
           <t xml:space="preserve">  ATTENTION NEEDED</t>
         </is>
@@ -2010,12 +2073,12 @@
     </row>
     <row r="50" ht="8" customHeight="1" s="28"/>
     <row r="51" ht="18" customHeight="1" s="28">
-      <c r="B51" s="128" t="inlineStr">
+      <c r="B51" s="149" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C51" s="128" t="inlineStr">
+      <c r="C51" s="149" t="inlineStr">
         <is>
           <t>Obligation</t>
         </is>
@@ -2025,26 +2088,26 @@
       <c r="F51" s="66" t="n"/>
       <c r="G51" s="66" t="n"/>
       <c r="H51" s="60" t="n"/>
-      <c r="I51" s="128" t="inlineStr">
+      <c r="I51" s="149" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
       <c r="J51" s="66" t="n"/>
       <c r="K51" s="60" t="n"/>
-      <c r="L51" s="128" t="inlineStr">
+      <c r="L51" s="149" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="M51" s="128" t="inlineStr">
+      <c r="M51" s="149" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1" s="28">
-      <c r="B52" s="134" t="inlineStr">
+      <c r="B52" s="155" t="inlineStr">
         <is>
           <t>OB-A2</t>
         </is>
@@ -2066,19 +2129,19 @@
       </c>
       <c r="J52" s="66" t="n"/>
       <c r="K52" s="60" t="n"/>
-      <c r="L52" s="130" t="inlineStr">
+      <c r="L52" s="151" t="inlineStr">
         <is>
           <t>24 Jun 2026</t>
         </is>
       </c>
-      <c r="M52" s="135" t="inlineStr">
+      <c r="M52" s="156" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="53" ht="34" customHeight="1" s="28">
-      <c r="B53" s="136" t="inlineStr">
+      <c r="B53" s="157" t="inlineStr">
         <is>
           <t>OB-A7</t>
         </is>
@@ -2100,19 +2163,19 @@
       </c>
       <c r="J53" s="66" t="n"/>
       <c r="K53" s="60" t="n"/>
-      <c r="L53" s="132" t="inlineStr">
+      <c r="L53" s="153" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="M53" s="137" t="inlineStr">
+      <c r="M53" s="158" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="54" ht="34" customHeight="1" s="28">
-      <c r="B54" s="134" t="inlineStr">
+      <c r="B54" s="155" t="inlineStr">
         <is>
           <t>OB-A9</t>
         </is>
@@ -2134,19 +2197,19 @@
       </c>
       <c r="J54" s="66" t="n"/>
       <c r="K54" s="60" t="n"/>
-      <c r="L54" s="130" t="inlineStr">
+      <c r="L54" s="151" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="M54" s="135" t="inlineStr">
+      <c r="M54" s="156" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="55" ht="34" customHeight="1" s="28">
-      <c r="B55" s="136" t="inlineStr">
+      <c r="B55" s="157" t="inlineStr">
         <is>
           <t>OB-A11</t>
         </is>
@@ -2168,19 +2231,19 @@
       </c>
       <c r="J55" s="66" t="n"/>
       <c r="K55" s="60" t="n"/>
-      <c r="L55" s="132" t="inlineStr">
+      <c r="L55" s="153" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="M55" s="137" t="inlineStr">
+      <c r="M55" s="158" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="56" ht="34" customHeight="1" s="28">
-      <c r="B56" s="134" t="inlineStr">
+      <c r="B56" s="155" t="inlineStr">
         <is>
           <t>OB-L5</t>
         </is>
@@ -2202,12 +2265,12 @@
       </c>
       <c r="J56" s="66" t="n"/>
       <c r="K56" s="60" t="n"/>
-      <c r="L56" s="130" t="inlineStr">
+      <c r="L56" s="151" t="inlineStr">
         <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="M56" s="135" t="inlineStr">
+      <c r="M56" s="156" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
@@ -2215,19 +2278,19 @@
     </row>
     <row r="57" ht="10" customHeight="1" s="28"/>
     <row r="58" ht="4" customHeight="1" s="28">
-      <c r="A58" s="117" t="n"/>
-      <c r="B58" s="117" t="n"/>
-      <c r="C58" s="117" t="n"/>
-      <c r="D58" s="117" t="n"/>
-      <c r="E58" s="117" t="n"/>
-      <c r="F58" s="117" t="n"/>
-      <c r="G58" s="117" t="n"/>
-      <c r="H58" s="117" t="n"/>
-      <c r="I58" s="117" t="n"/>
-      <c r="J58" s="117" t="n"/>
-      <c r="K58" s="117" t="n"/>
-      <c r="L58" s="117" t="n"/>
-      <c r="M58" s="117" t="n"/>
+      <c r="A58" s="138" t="n"/>
+      <c r="B58" s="138" t="n"/>
+      <c r="C58" s="138" t="n"/>
+      <c r="D58" s="138" t="n"/>
+      <c r="E58" s="138" t="n"/>
+      <c r="F58" s="138" t="n"/>
+      <c r="G58" s="138" t="n"/>
+      <c r="H58" s="138" t="n"/>
+      <c r="I58" s="138" t="n"/>
+      <c r="J58" s="138" t="n"/>
+      <c r="K58" s="138" t="n"/>
+      <c r="L58" s="138" t="n"/>
+      <c r="M58" s="138" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="61">
@@ -14766,7 +14829,7 @@
       </c>
       <c r="O8" s="44" t="inlineStr">
         <is>
-          <t>A-014</t>
+          <t>A-014, A-034</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14900,7 @@
       </c>
       <c r="O9" s="46" t="inlineStr">
         <is>
-          <t>A-015</t>
+          <t>A-015, A-035</t>
         </is>
       </c>
     </row>
@@ -15894,7 +15957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="28" min="1" max="1"/>
@@ -16154,7 +16217,7 @@
       </c>
       <c r="C6" s="44" t="inlineStr">
         <is>
-          <t>Prepare an Audit Committee briefing note on the LAO transition and its implications for NCC's PSAA-procured contract to 2027/28.</t>
+          <t>Prepare an Audit Committee briefing note on the LAO transition and its implications for NCC's PSAA-procured audit contract, which now runs to 2030.</t>
         </is>
       </c>
       <c r="D6" s="44" t="inlineStr">
@@ -16174,10 +16237,14 @@
       <c r="H6" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="44" t="inlineStr"/>
+      <c r="I6" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6926f871345e31ab14ecf524/Local_Audit_Transition_Plan.pdf</t>
+        </is>
+      </c>
       <c r="J6" s="44" t="inlineStr">
         <is>
-          <t>Supports OB-A10. Note Bill Butler as preferred LAO Chair candidate (May 2026).</t>
+          <t>Supports OB-A10. Milestones from the MHCLG Local Audit Transition Plan (Nov 2025), Annex A: LAO legally established Autumn 2026; auditor appointment and contracting duties, PSAA staff and the existing contracts transfer to the LAO Spring 2027. Bill Butler CONFIRMED as LAO Chair from 1 July 2026 (was recorded as preferred candidate).</t>
         </is>
       </c>
       <c r="K6" s="44" t="n"/>
@@ -17383,9 +17450,108 @@
       <c r="K33" s="46" t="n"/>
       <c r="L33" s="46" t="n"/>
     </row>
+    <row r="34" ht="40" customHeight="1" s="28">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>A-034</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>OB-A7</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>Confirm whether NCC gave MHCLG permission for its auditor to share the Auditor's Annual Report, the ISA 260 and the audit capacity assessment with the Department, and resolve the position with MHCLG if it did not.</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
+        </is>
+      </c>
+      <c r="E34" s="73" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F34" s="73" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G34" s="43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H34" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="44" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/692992e6a245b0985f034280/Ministerial_letter_to_local_bodies.pdf</t>
+        </is>
+      </c>
+      <c r="J34" s="44" t="inlineStr">
+        <is>
+          <t>RETROSPECTIVE CHECK — BOTH DEADLINES HAVE PASSED. The Minister of State wrote to Chief Executives, CFOs and Leaders on 27 November 2025 asking for the AAR and ISA 260 by 31 March 2026 and an auditor capacity assessment by end July 2026. The letter says that where permission is not given, MHCLG officials will follow up directly. There is no record either way in the tracker, so the answer needs establishing rather than assuming. Evidence: the permission response to the audit firm, or correspondence with MHCLG.</t>
+        </is>
+      </c>
+      <c r="K34" s="44" t="n"/>
+      <c r="L34" s="44" t="n"/>
+    </row>
+    <row r="35" ht="40" customHeight="1" s="28">
+      <c r="A35" s="46" t="inlineStr">
+        <is>
+          <t>A-035</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>OB-A8</t>
+        </is>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>Agree the build-back trajectory with the external auditor for clearing any backstop-related disclaimed opinions, working to the 30 November 2028 backstop, and report the trajectory to the Audit Committee.</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="inlineStr">
+        <is>
+          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
+        </is>
+      </c>
+      <c r="E35" s="74" t="n">
+        <v>46238</v>
+      </c>
+      <c r="F35" s="74" t="n">
+        <v>46353</v>
+      </c>
+      <c r="G35" s="45" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="46" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/692992e6a245b0985f034280/Ministerial_letter_to_local_bodies.pdf</t>
+        </is>
+      </c>
+      <c r="J35" s="46" t="inlineStr">
+        <is>
+          <t>The build-back programme aims to clear backstop-related disclaimers by the end of 2027/28, for which the backstop date is 30 November 2028. Government has said progress is slower than hoped and that NO FURTHER build-back grant was paid in 2025/26, with the funding model reviewed in summer and autumn 2026 — so the cost of this sits with NCC unless that review changes it. The letter also stresses that authorities must adequately resource their finance functions to supply audit evidence.</t>
+        </is>
+      </c>
+      <c r="K35" s="46" t="n"/>
+      <c r="L35" s="46" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L33"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:L35"/>
+  <dataValidations count="4">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Complete,Blocked,Cancelled"</formula1>
+    </dataValidation>
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Complete,Blocked,Cancelled"</formula1>
     </dataValidation>
@@ -17407,14 +17573,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="28" min="1" max="2"/>
+    <col width="18" customWidth="1" style="28" min="1" max="1"/>
     <col width="18" customWidth="1" style="28" min="2" max="2"/>
     <col width="22" customWidth="1" style="28" min="3" max="3"/>
     <col width="50" customWidth="1" style="28" min="4" max="4"/>
-    <col width="18" customWidth="1" style="28" min="5" max="8"/>
+    <col width="18" customWidth="1" style="28" min="5" max="5"/>
     <col width="18" customWidth="1" style="28" min="6" max="6"/>
     <col width="18" customWidth="1" style="28" min="7" max="7"/>
     <col width="18" customWidth="1" style="28" min="8" max="8"/>
@@ -17498,7 +17664,7 @@
           <t>Audit Committee papers</t>
         </is>
       </c>
-      <c r="H2" s="44" t="n"/>
+      <c r="H2" s="44" t="inlineStr"/>
     </row>
     <row r="3" ht="40" customHeight="1" s="28">
       <c r="A3" s="46" t="inlineStr">
@@ -17536,7 +17702,7 @@
           <t>Audit Committee papers</t>
         </is>
       </c>
-      <c r="H3" s="46" t="n"/>
+      <c r="H3" s="46" t="inlineStr"/>
     </row>
     <row r="4" ht="40" customHeight="1" s="28">
       <c r="A4" s="44" t="inlineStr">
@@ -17574,7 +17740,7 @@
           <t>Audit Committee papers</t>
         </is>
       </c>
-      <c r="H4" s="44" t="n"/>
+      <c r="H4" s="44" t="inlineStr"/>
     </row>
     <row r="5" ht="40" customHeight="1" s="28">
       <c r="A5" s="46" t="inlineStr">
@@ -17602,13 +17768,13 @@
           <t>Section 151 Officer / Audit Committee</t>
         </is>
       </c>
-      <c r="F5" s="46" t="n"/>
+      <c r="F5" s="46" t="inlineStr"/>
       <c r="G5" s="46" t="inlineStr">
         <is>
           <t>Audit Committee papers</t>
         </is>
       </c>
-      <c r="H5" s="46" t="n"/>
+      <c r="H5" s="46" t="inlineStr"/>
     </row>
     <row r="6" ht="40" customHeight="1" s="28">
       <c r="A6" s="44" t="inlineStr">
@@ -17646,7 +17812,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H6" s="44" t="n"/>
+      <c r="H6" s="44" t="inlineStr"/>
     </row>
     <row r="7" ht="40" customHeight="1" s="28">
       <c r="A7" s="46" t="inlineStr">
@@ -17684,7 +17850,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H7" s="46" t="n"/>
+      <c r="H7" s="46" t="inlineStr"/>
     </row>
     <row r="8" ht="40" customHeight="1" s="28">
       <c r="A8" s="44" t="inlineStr">
@@ -17722,7 +17888,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H8" s="44" t="n"/>
+      <c r="H8" s="44" t="inlineStr"/>
     </row>
     <row r="9" ht="40" customHeight="1" s="28">
       <c r="A9" s="46" t="inlineStr">
@@ -17732,7 +17898,7 @@
       </c>
       <c r="B9" s="46" t="inlineStr">
         <is>
-          <t>A-005</t>
+          <t>A-006</t>
         </is>
       </c>
       <c r="C9" s="46" t="inlineStr">
@@ -17742,12 +17908,12 @@
       </c>
       <c r="D9" s="46" t="inlineStr">
         <is>
-          <t>Prepare an Audit Committee briefing note on the LAO transition and its implications for NCC's PSAA-procured contract to 2027/28.</t>
+          <t>Review structural transitional reporting regulations issued by the preferred LAO Chair candidate and adjust internal audit backstop clearance mileston</t>
         </is>
       </c>
       <c r="E9" s="46" t="inlineStr">
         <is>
-          <t>OB-A10</t>
+          <t>OB-A12</t>
         </is>
       </c>
       <c r="F9" s="46" t="inlineStr">
@@ -17760,7 +17926,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H9" s="46" t="n"/>
+      <c r="H9" s="46" t="inlineStr"/>
     </row>
     <row r="10" ht="40" customHeight="1" s="28">
       <c r="A10" s="44" t="inlineStr">
@@ -17770,27 +17936,27 @@
       </c>
       <c r="B10" s="44" t="inlineStr">
         <is>
-          <t>A-006</t>
+          <t>A-007</t>
         </is>
       </c>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>Lynne Dowdican (Head of Internal Audit)</t>
+          <t>James Rhodes (Director of Policy, Performance and Communications)</t>
         </is>
       </c>
       <c r="D10" s="44" t="inlineStr">
         <is>
-          <t>Review structural transitional reporting regulations issued by the preferred LAO Chair candidate and adjust internal audit backstop clearance mileston</t>
+          <t>Perform an internal option appraisal to cross-examine whether the newly introduced June 2026 GOV.UK reorganisation layout guidance changes boundary li</t>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>OB-A12</t>
+          <t>OB-L7</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G10" s="44" t="inlineStr">
@@ -17798,7 +17964,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H10" s="44" t="n"/>
+      <c r="H10" s="44" t="inlineStr"/>
     </row>
     <row r="11" ht="40" customHeight="1" s="28">
       <c r="A11" s="46" t="inlineStr">
@@ -17808,27 +17974,27 @@
       </c>
       <c r="B11" s="46" t="inlineStr">
         <is>
-          <t>A-007</t>
+          <t>A-008</t>
         </is>
       </c>
       <c r="C11" s="46" t="inlineStr">
         <is>
-          <t>James Rhodes (Director of Policy, Performance and Communications)</t>
+          <t>Beth Brown (Strategic Director of Legal and Governance)</t>
         </is>
       </c>
       <c r="D11" s="46" t="inlineStr">
         <is>
-          <t>Perform an internal option appraisal to cross-examine whether the newly introduced June 2026 GOV.UK reorganisation layout guidance changes boundary li</t>
+          <t>Draft the formal accountability framework and code alignment overview mandated by the recent Royal Assent confirmation of the English Devolution Act.</t>
         </is>
       </c>
       <c r="E11" s="46" t="inlineStr">
         <is>
-          <t>OB-L7</t>
+          <t>OB-L5</t>
         </is>
       </c>
       <c r="F11" s="46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G11" s="46" t="inlineStr">
@@ -17836,7 +18002,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H11" s="46" t="n"/>
+      <c r="H11" s="46" t="inlineStr"/>
     </row>
     <row r="12" ht="40" customHeight="1" s="28">
       <c r="A12" s="44" t="inlineStr">
@@ -17846,27 +18012,27 @@
       </c>
       <c r="B12" s="44" t="inlineStr">
         <is>
-          <t>A-008</t>
+          <t>A-009</t>
         </is>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>Beth Brown (Strategic Director of Legal and Governance)</t>
+          <t>Sajeeda Rose (Chief Executive)</t>
         </is>
       </c>
       <c r="D12" s="44" t="inlineStr">
         <is>
-          <t>Draft the formal accountability framework and code alignment overview mandated by the recent Royal Assent confirmation of the English Devolution Act.</t>
+          <t>Coordinate final verification review and ensure physical sign-off endorsement of the complete CSIP text block by Ministerial Envoys.</t>
         </is>
       </c>
       <c r="E12" s="44" t="inlineStr">
         <is>
-          <t>OB-L5</t>
+          <t>OB-A2</t>
         </is>
       </c>
       <c r="F12" s="44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G12" s="44" t="inlineStr">
@@ -17874,7 +18040,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H12" s="44" t="n"/>
+      <c r="H12" s="44" t="inlineStr"/>
     </row>
     <row r="13" ht="40" customHeight="1" s="28">
       <c r="A13" s="46" t="inlineStr">
@@ -17884,27 +18050,27 @@
       </c>
       <c r="B13" s="46" t="inlineStr">
         <is>
-          <t>A-009</t>
+          <t>A-010</t>
         </is>
       </c>
       <c r="C13" s="46" t="inlineStr">
         <is>
-          <t>Sajeeda Rose (Chief Executive)</t>
+          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
         </is>
       </c>
       <c r="D13" s="46" t="inlineStr">
         <is>
-          <t>Coordinate final verification review and ensure physical sign-off endorsement of the complete CSIP text block by Ministerial Envoys.</t>
+          <t>Review financial management, savings delivery, accounts production, and capital programme improvements at the six-monthly Improvement Committee report</t>
         </is>
       </c>
       <c r="E13" s="46" t="inlineStr">
         <is>
-          <t>OB-A2</t>
+          <t>OB-A3</t>
         </is>
       </c>
       <c r="F13" s="46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G13" s="46" t="inlineStr">
@@ -17912,7 +18078,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H13" s="46" t="n"/>
+      <c r="H13" s="46" t="inlineStr"/>
     </row>
     <row r="14" ht="40" customHeight="1" s="28">
       <c r="A14" s="44" t="inlineStr">
@@ -17922,22 +18088,22 @@
       </c>
       <c r="B14" s="44" t="inlineStr">
         <is>
-          <t>A-010</t>
+          <t>A-011</t>
         </is>
       </c>
       <c r="C14" s="44" t="inlineStr">
         <is>
-          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
+          <t>Beth Brown (Strategic Director of Legal and Governance)</t>
         </is>
       </c>
       <c r="D14" s="44" t="inlineStr">
         <is>
-          <t>Review financial management, savings delivery, accounts production, and capital programme improvements at the six-monthly Improvement Committee report</t>
+          <t>Review scrutiny and decision-making improvements at each Improvement Committee report and record the check, filing Corporate Scrutiny papers and Schem</t>
         </is>
       </c>
       <c r="E14" s="44" t="inlineStr">
         <is>
-          <t>OB-A3</t>
+          <t>OB-A4</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
@@ -17950,7 +18116,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H14" s="44" t="n"/>
+      <c r="H14" s="44" t="inlineStr"/>
     </row>
     <row r="15" ht="40" customHeight="1" s="28">
       <c r="A15" s="46" t="inlineStr">
@@ -17960,27 +18126,27 @@
       </c>
       <c r="B15" s="46" t="inlineStr">
         <is>
-          <t>A-011</t>
+          <t>A-012</t>
         </is>
       </c>
       <c r="C15" s="46" t="inlineStr">
         <is>
-          <t>Beth Brown (Strategic Director of Legal and Governance)</t>
+          <t>Lynne Dowdican (Head of Internal Audit)</t>
         </is>
       </c>
       <c r="D15" s="46" t="inlineStr">
         <is>
-          <t>Review scrutiny and decision-making improvements at each Improvement Committee report and record the check, filing Corporate Scrutiny papers and Schem</t>
+          <t>Prepare the internal audit alignment note against Local Audit Office standards and guidance, and present progress reports at each Audit Committee.</t>
         </is>
       </c>
       <c r="E15" s="46" t="inlineStr">
         <is>
-          <t>OB-A4</t>
+          <t>OB-A5</t>
         </is>
       </c>
       <c r="F15" s="46" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G15" s="46" t="inlineStr">
@@ -17988,7 +18154,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H15" s="46" t="n"/>
+      <c r="H15" s="46" t="inlineStr"/>
     </row>
     <row r="16" ht="40" customHeight="1" s="28">
       <c r="A16" s="44" t="inlineStr">
@@ -17998,27 +18164,27 @@
       </c>
       <c r="B16" s="44" t="inlineStr">
         <is>
-          <t>A-012</t>
+          <t>A-013</t>
         </is>
       </c>
       <c r="C16" s="44" t="inlineStr">
         <is>
-          <t>Lynne Dowdican (Head of Internal Audit)</t>
+          <t>Sajeeda Rose (Chief Executive)</t>
         </is>
       </c>
       <c r="D16" s="44" t="inlineStr">
         <is>
-          <t>Prepare the internal audit alignment note against Local Audit Office standards and guidance, and present progress reports at each Audit Committee.</t>
+          <t>Record Ministerial Envoy attendance and the council's responses to Envoy recommendations at each Improvement Committee meeting.</t>
         </is>
       </c>
       <c r="E16" s="44" t="inlineStr">
         <is>
-          <t>OB-A5</t>
+          <t>OB-A6</t>
         </is>
       </c>
       <c r="F16" s="44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G16" s="44" t="inlineStr">
@@ -18026,7 +18192,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H16" s="44" t="n"/>
+      <c r="H16" s="44" t="inlineStr"/>
     </row>
     <row r="17" ht="40" customHeight="1" s="28">
       <c r="A17" s="46" t="inlineStr">
@@ -18036,27 +18202,27 @@
       </c>
       <c r="B17" s="46" t="inlineStr">
         <is>
-          <t>A-013</t>
+          <t>A-014</t>
         </is>
       </c>
       <c r="C17" s="46" t="inlineStr">
         <is>
-          <t>Sajeeda Rose (Chief Executive)</t>
+          <t>Gareth Robinson (Director of Finance)</t>
         </is>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
-          <t>Record Ministerial Envoy attendance and the council's responses to Envoy recommendations at each Improvement Committee meeting.</t>
+          <t>Produce the management response document to each recommendation in the external auditor's Annual Report (ISA 260) and secure the Audit Committee accep</t>
         </is>
       </c>
       <c r="E17" s="46" t="inlineStr">
         <is>
-          <t>OB-A6</t>
+          <t>OB-A7</t>
         </is>
       </c>
       <c r="F17" s="46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G17" s="46" t="inlineStr">
@@ -18064,7 +18230,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H17" s="46" t="n"/>
+      <c r="H17" s="46" t="inlineStr"/>
     </row>
     <row r="18" ht="40" customHeight="1" s="28">
       <c r="A18" s="44" t="inlineStr">
@@ -18074,27 +18240,27 @@
       </c>
       <c r="B18" s="44" t="inlineStr">
         <is>
-          <t>A-014</t>
+          <t>A-015</t>
         </is>
       </c>
       <c r="C18" s="44" t="inlineStr">
         <is>
-          <t>Gareth Robinson (Director of Finance)</t>
+          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
         </is>
       </c>
       <c r="D18" s="44" t="inlineStr">
         <is>
-          <t>Produce the management response document to each recommendation in the external auditor's Annual Report (ISA 260) and secure the Audit Committee accep</t>
+          <t>Produce and publish the 2024/25 Statement of Accounts with the auditor's opinion (noting any disclaimer), and link the specific year's document on the</t>
         </is>
       </c>
       <c r="E18" s="44" t="inlineStr">
         <is>
-          <t>OB-A7</t>
+          <t>OB-A8</t>
         </is>
       </c>
       <c r="F18" s="44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G18" s="44" t="inlineStr">
@@ -18102,7 +18268,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H18" s="44" t="n"/>
+      <c r="H18" s="44" t="inlineStr"/>
     </row>
     <row r="19" ht="40" customHeight="1" s="28">
       <c r="A19" s="46" t="inlineStr">
@@ -18112,27 +18278,27 @@
       </c>
       <c r="B19" s="46" t="inlineStr">
         <is>
-          <t>A-015</t>
+          <t>A-016</t>
         </is>
       </c>
       <c r="C19" s="46" t="inlineStr">
         <is>
-          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
+          <t>Beth Brown (Strategic Director of Legal and Governance)</t>
         </is>
       </c>
       <c r="D19" s="46" t="inlineStr">
         <is>
-          <t>Produce and publish the 2024/25 Statement of Accounts with the auditor's opinion (noting any disclaimer), and link the specific year's document on the</t>
+          <t>Secure Audit Committee approval of the published draft Annual Governance Statement 2024/25 and link the approval minute as evidence.</t>
         </is>
       </c>
       <c r="E19" s="46" t="inlineStr">
         <is>
-          <t>OB-A8</t>
+          <t>OB-A9</t>
         </is>
       </c>
       <c r="F19" s="46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G19" s="46" t="inlineStr">
@@ -18140,7 +18306,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H19" s="46" t="n"/>
+      <c r="H19" s="46" t="inlineStr"/>
     </row>
     <row r="20" ht="40" customHeight="1" s="28">
       <c r="A20" s="44" t="inlineStr">
@@ -18150,27 +18316,27 @@
       </c>
       <c r="B20" s="44" t="inlineStr">
         <is>
-          <t>A-016</t>
+          <t>A-017</t>
         </is>
       </c>
       <c r="C20" s="44" t="inlineStr">
         <is>
-          <t>Beth Brown (Strategic Director of Legal and Governance)</t>
+          <t>James Rhodes (Director of Policy, Performance and Communications)</t>
         </is>
       </c>
       <c r="D20" s="44" t="inlineStr">
         <is>
-          <t>Secure Audit Committee approval of the published draft Annual Governance Statement 2024/25 and link the approval minute as evidence.</t>
+          <t>File joint LGR committee papers, transition programme updates to the Improvement Committee, and cooperation records with the other Nottinghamshire cou</t>
         </is>
       </c>
       <c r="E20" s="44" t="inlineStr">
         <is>
-          <t>OB-A9</t>
+          <t>OB-L1</t>
         </is>
       </c>
       <c r="F20" s="44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G20" s="44" t="inlineStr">
@@ -18178,7 +18344,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H20" s="44" t="n"/>
+      <c r="H20" s="44" t="inlineStr"/>
     </row>
     <row r="21" ht="40" customHeight="1" s="28">
       <c r="A21" s="46" t="inlineStr">
@@ -18188,27 +18354,27 @@
       </c>
       <c r="B21" s="46" t="inlineStr">
         <is>
-          <t>A-017</t>
+          <t>A-019</t>
         </is>
       </c>
       <c r="C21" s="46" t="inlineStr">
         <is>
-          <t>James Rhodes (Director of Policy, Performance and Communications)</t>
+          <t>Lynne Dowdican (Head of Internal Audit)</t>
         </is>
       </c>
       <c r="D21" s="46" t="inlineStr">
         <is>
-          <t>File joint LGR committee papers, transition programme updates to the Improvement Committee, and cooperation records with the other Nottinghamshire cou</t>
+          <t>Update the Internal Audit Annual Plan with an LGR transition risk section (service demerger, asset and liability transfer, shadow authority governance</t>
         </is>
       </c>
       <c r="E21" s="46" t="inlineStr">
         <is>
-          <t>OB-L1</t>
+          <t>OB-L4</t>
         </is>
       </c>
       <c r="F21" s="46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="G21" s="46" t="inlineStr">
@@ -18216,7 +18382,7 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H21" s="46" t="n"/>
+      <c r="H21" s="46" t="inlineStr"/>
     </row>
     <row r="22" ht="40" customHeight="1" s="28">
       <c r="A22" s="44" t="inlineStr">
@@ -18226,35 +18392,31 @@
       </c>
       <c r="B22" s="44" t="inlineStr">
         <is>
-          <t>A-019</t>
+          <t>A-020</t>
         </is>
       </c>
       <c r="C22" s="44" t="inlineStr">
         <is>
-          <t>Lynne Dowdican (Head of Internal Audit)</t>
+          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
         </is>
       </c>
       <c r="D22" s="44" t="inlineStr">
         <is>
-          <t>Update the Internal Audit Annual Plan with an LGR transition risk section (service demerger, asset and liability transfer, shadow authority governance</t>
+          <t>On issue of the final Statutory Boundary Order, complete the Section 151 review of asset and liability transfer arrangements and report to the Audit /</t>
         </is>
       </c>
       <c r="E22" s="44" t="inlineStr">
         <is>
-          <t>OB-L4</t>
-        </is>
-      </c>
-      <c r="F22" s="44" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
+          <t>OB-L6</t>
+        </is>
+      </c>
+      <c r="F22" s="44" t="inlineStr"/>
       <c r="G22" s="44" t="inlineStr">
         <is>
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H22" s="44" t="n"/>
+      <c r="H22" s="44" t="inlineStr"/>
     </row>
     <row r="23" ht="40" customHeight="1" s="28">
       <c r="A23" s="46" t="inlineStr">
@@ -18264,31 +18426,31 @@
       </c>
       <c r="B23" s="46" t="inlineStr">
         <is>
-          <t>A-020</t>
+          <t>A-021</t>
         </is>
       </c>
       <c r="C23" s="46" t="inlineStr">
         <is>
-          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
+          <t>James Rhodes (Director of Policy, Performance and Communications)</t>
         </is>
       </c>
       <c r="D23" s="46" t="inlineStr">
         <is>
-          <t>On issue of the final Statutory Boundary Order, complete the Section 151 review of asset and liability transfer arrangements and report to the Audit /</t>
+          <t>Participate in joint implementation governance.</t>
         </is>
       </c>
       <c r="E23" s="46" t="inlineStr">
         <is>
-          <t>OB-L6</t>
-        </is>
-      </c>
-      <c r="F23" s="46" t="n"/>
+          <t>OB-L1</t>
+        </is>
+      </c>
+      <c r="F23" s="46" t="inlineStr"/>
       <c r="G23" s="46" t="inlineStr">
         <is>
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H23" s="46" t="n"/>
+      <c r="H23" s="46" t="inlineStr"/>
     </row>
     <row r="24" ht="40" customHeight="1" s="28">
       <c r="A24" s="44" t="inlineStr">
@@ -18298,7 +18460,7 @@
       </c>
       <c r="B24" s="44" t="inlineStr">
         <is>
-          <t>A-021</t>
+          <t>A-022</t>
         </is>
       </c>
       <c r="C24" s="44" t="inlineStr">
@@ -18308,7 +18470,7 @@
       </c>
       <c r="D24" s="44" t="inlineStr">
         <is>
-          <t>Participate in joint implementation governance.</t>
+          <t>Work with Nottinghamshire authorities on transition arrangements.</t>
         </is>
       </c>
       <c r="E24" s="44" t="inlineStr">
@@ -18316,13 +18478,13 @@
           <t>OB-L1</t>
         </is>
       </c>
-      <c r="F24" s="44" t="n"/>
+      <c r="F24" s="44" t="inlineStr"/>
       <c r="G24" s="44" t="inlineStr">
         <is>
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H24" s="44" t="n"/>
+      <c r="H24" s="44" t="inlineStr"/>
     </row>
     <row r="25" ht="40" customHeight="1" s="28">
       <c r="A25" s="46" t="inlineStr">
@@ -18332,17 +18494,17 @@
       </c>
       <c r="B25" s="46" t="inlineStr">
         <is>
-          <t>A-022</t>
+          <t>A-023</t>
         </is>
       </c>
       <c r="C25" s="46" t="inlineStr">
         <is>
-          <t>James Rhodes (Director of Policy, Performance and Communications)</t>
+          <t>Lee Mann (Strategic Director of HR &amp; EDI)</t>
         </is>
       </c>
       <c r="D25" s="46" t="inlineStr">
         <is>
-          <t>Work with Nottinghamshire authorities on transition arrangements.</t>
+          <t>Support development of new operating models, staffing arrangements and service integration plans.</t>
         </is>
       </c>
       <c r="E25" s="46" t="inlineStr">
@@ -18350,13 +18512,13 @@
           <t>OB-L1</t>
         </is>
       </c>
-      <c r="F25" s="46" t="n"/>
+      <c r="F25" s="46" t="inlineStr"/>
       <c r="G25" s="46" t="inlineStr">
         <is>
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H25" s="46" t="n"/>
+      <c r="H25" s="46" t="inlineStr"/>
     </row>
     <row r="26" ht="40" customHeight="1" s="28">
       <c r="A26" s="44" t="inlineStr">
@@ -18366,31 +18528,35 @@
       </c>
       <c r="B26" s="44" t="inlineStr">
         <is>
-          <t>A-023</t>
+          <t>A-028</t>
         </is>
       </c>
       <c r="C26" s="44" t="inlineStr">
         <is>
-          <t>Lee Mann (Strategic Director of HR &amp; EDI)</t>
+          <t>Beth Brown (Strategic Director of Legal and Governance)</t>
         </is>
       </c>
       <c r="D26" s="44" t="inlineStr">
         <is>
-          <t>Support development of new operating models, staffing arrangements and service integration plans.</t>
+          <t>Launch recruitment for an independent member of the Audit Committee, including a public advertisement and role profile, ahead of the membership regula</t>
         </is>
       </c>
       <c r="E26" s="44" t="inlineStr">
         <is>
-          <t>OB-L1</t>
-        </is>
-      </c>
-      <c r="F26" s="44" t="n"/>
+          <t>OB-A13</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="G26" s="44" t="inlineStr">
         <is>
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H26" s="44" t="n"/>
+      <c r="H26" s="44" t="inlineStr"/>
     </row>
     <row r="27" ht="40" customHeight="1" s="28">
       <c r="A27" s="46" t="inlineStr">
@@ -18400,17 +18566,17 @@
       </c>
       <c r="B27" s="46" t="inlineStr">
         <is>
-          <t>A-028</t>
+          <t>A-029</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
         <is>
-          <t>Beth Brown (Strategic Director of Legal and Governance)</t>
+          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
         </is>
       </c>
       <c r="D27" s="46" t="inlineStr">
         <is>
-          <t>Launch recruitment for an independent member of the Audit Committee, including a public advertisement and role profile, ahead of the membership regula</t>
+          <t>Monitor for the s.94 regulations on audit committee membership, appointments and allowances, and the statutory guidance that follows them; on publicat</t>
         </is>
       </c>
       <c r="E27" s="46" t="inlineStr">
@@ -18418,17 +18584,13 @@
           <t>OB-A13</t>
         </is>
       </c>
-      <c r="F27" s="46" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="F27" s="46" t="inlineStr"/>
       <c r="G27" s="46" t="inlineStr">
         <is>
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H27" s="46" t="n"/>
+      <c r="H27" s="46" t="inlineStr"/>
     </row>
     <row r="28" ht="40" customHeight="1" s="28">
       <c r="A28" s="44" t="inlineStr">
@@ -18438,31 +18600,35 @@
       </c>
       <c r="B28" s="44" t="inlineStr">
         <is>
-          <t>A-029</t>
+          <t>A-030</t>
         </is>
       </c>
       <c r="C28" s="44" t="inlineStr">
         <is>
-          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
+          <t>Sajeeda Rose (Chief Executive)</t>
         </is>
       </c>
       <c r="D28" s="44" t="inlineStr">
         <is>
-          <t>Monitor for the s.94 regulations on audit committee membership, appointments and allowances, and the statutory guidance that follows them; on publicat</t>
+          <t>Coordinate the initial political and executive induction sessions with Political Envoy Sir Stephen Houghton CBE.</t>
         </is>
       </c>
       <c r="E28" s="44" t="inlineStr">
         <is>
-          <t>OB-A13</t>
-        </is>
-      </c>
-      <c r="F28" s="44" t="n"/>
+          <t>OB-A14</t>
+        </is>
+      </c>
+      <c r="F28" s="44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="G28" s="44" t="inlineStr">
         <is>
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H28" s="44" t="n"/>
+      <c r="H28" s="44" t="inlineStr"/>
     </row>
     <row r="29" ht="40" customHeight="1" s="28">
       <c r="A29" s="46" t="inlineStr">
@@ -18472,17 +18638,17 @@
       </c>
       <c r="B29" s="46" t="inlineStr">
         <is>
-          <t>A-030</t>
+          <t>A-032</t>
         </is>
       </c>
       <c r="C29" s="46" t="inlineStr">
         <is>
-          <t>Sajeeda Rose (Chief Executive)</t>
+          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
         </is>
       </c>
       <c r="D29" s="46" t="inlineStr">
         <is>
-          <t>Coordinate the initial political and executive induction sessions with Political Envoy Sir Stephen Houghton CBE.</t>
+          <t>Confirm budget provision for Political Envoy fees and expenses, and put in place the approval route for exceeding the 75-day annual cap.</t>
         </is>
       </c>
       <c r="E29" s="46" t="inlineStr">
@@ -18492,7 +18658,7 @@
       </c>
       <c r="F29" s="46" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G29" s="46" t="inlineStr">
@@ -18500,48 +18666,10 @@
           <t>Internal - council document store</t>
         </is>
       </c>
-      <c r="H29" s="46" t="n"/>
-    </row>
-    <row r="30" ht="40" customHeight="1" s="28">
-      <c r="A30" s="44" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B30" s="44" t="inlineStr">
-        <is>
-          <t>A-032</t>
-        </is>
-      </c>
-      <c r="C30" s="44" t="inlineStr">
-        <is>
-          <t>Stuart Fair (Corporate Director for Finance and Resources, S151)</t>
-        </is>
-      </c>
-      <c r="D30" s="44" t="inlineStr">
-        <is>
-          <t>Confirm budget provision for Political Envoy fees and expenses, and put in place the approval route for exceeding the 75-day annual cap.</t>
-        </is>
-      </c>
-      <c r="E30" s="44" t="inlineStr">
-        <is>
-          <t>OB-A14</t>
-        </is>
-      </c>
-      <c r="F30" s="44" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G30" s="44" t="inlineStr">
-        <is>
-          <t>Internal - council document store</t>
-        </is>
-      </c>
-      <c r="H30" s="44" t="n"/>
+      <c r="H29" s="46" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>